--- a/log_feature_extraction.xlsx
+++ b/log_feature_extraction.xlsx
@@ -2,14 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -49,7 +50,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -412,11 +413,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CF5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
-  <cols>
-    <col width="37.44140625" customWidth="1" min="2" max="2"/>
-  </cols>
+  <dimension ref="A1:CG3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -426,7 +424,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>LINK</t>
+          <t>URL</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -436,405 +434,410 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>STATUS</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>length_url</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>length_hostname</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ip</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>nb_dots</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>nb_hyphens</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>nb_at</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>nb_qm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>nb_and</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>nb_eq</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>nb_underscore</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>nb_tilde</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>nb_percent</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>nb_slash</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>nb_star</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>nb_colon</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>nb_comma</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>nb_semicolumn</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>nb_dollar</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>nb_space</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>nb_www</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>nb_com</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>nb_dslash</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>http_in_path</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>https_token</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>ratio_digits_url</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>ratio_digits_host</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>punycode</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>port</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>tld_in_path</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>tld_in_subdomain</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>abnormal_subdomain</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>nb_subdomains</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>prefix_suffix</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>random_domain</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>shortening_service</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>path_extension</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>nb_redirection</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>nb_external_redirection</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>length_words_raw</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>char_repeat</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>shortest_words_raw</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>shortest_word_host</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>shortest_word_path</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>longest_words_raw</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>longest_word_host</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>longest_word_path</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>avg_words_raw</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>avg_word_host</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>avg_word_path</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>phish_hints</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>domain_in_brand</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>brand_in_subdomain</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>brand_in_path</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>suspicious_tld</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>statistical_report</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>nb_hyperlinks</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>ratio_intHyperlinks</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>ratio_extHyperlinks</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>nb_extCSS</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>ratio_extRedirection</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>ratio_extErrors</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>login_form</t>
         </is>
       </c>
-      <c r="BN1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>external_favicon</t>
         </is>
       </c>
-      <c r="BO1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>links_in_tags</t>
         </is>
       </c>
-      <c r="BP1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>ratio_intMedia</t>
         </is>
       </c>
-      <c r="BQ1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>ratio_extMedia</t>
         </is>
       </c>
-      <c r="BR1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>iframe</t>
         </is>
       </c>
-      <c r="BS1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>popup_window</t>
         </is>
       </c>
-      <c r="BT1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>safe_anchor</t>
         </is>
       </c>
-      <c r="BU1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>onmouseover</t>
         </is>
       </c>
-      <c r="BV1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>right_clic</t>
         </is>
       </c>
-      <c r="BW1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>empty_title</t>
         </is>
       </c>
-      <c r="BX1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>domain_in_title</t>
         </is>
       </c>
-      <c r="BY1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>domain_with_copyright</t>
         </is>
       </c>
-      <c r="BZ1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>whois_registered_domain</t>
         </is>
       </c>
-      <c r="CA1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>domain_registration_length</t>
         </is>
       </c>
-      <c r="CB1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>domain_age</t>
         </is>
       </c>
-      <c r="CC1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>web_traffic</t>
         </is>
       </c>
-      <c r="CD1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>dns_record</t>
         </is>
       </c>
-      <c r="CE1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>google_index</t>
         </is>
       </c>
-      <c r="CF1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>page_rank</t>
         </is>
@@ -846,7 +849,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.google.com</t>
+          <t>https://www.microsoft.com</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -854,21 +857,23 @@
           <t>37</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>22</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
       </c>
       <c r="E2" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
         <v>2</v>
       </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
@@ -891,16 +896,16 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
         <v>2</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -912,7 +917,7 @@
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
         <v>1</v>
@@ -921,7 +926,7 @@
         <v>1</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -948,10 +953,10 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
@@ -960,7 +965,7 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN2" t="n">
         <v>0</v>
@@ -969,37 +974,37 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="n">
         <v>4</v>
       </c>
-      <c r="AQ2" t="n">
-        <v>5</v>
-      </c>
       <c r="AR2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS2" t="n">
         <v>3</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AX2" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BA2" t="n">
         <v>0</v>
@@ -1008,7 +1013,7 @@
         <v>1</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD2" t="n">
         <v>0</v>
@@ -1095,6 +1100,9 @@
         <v>0</v>
       </c>
       <c r="CF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1104,32 +1112,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://smmhejtkx.olghvlbkcdqtscd.top/ksjdbj</t>
+          <t>www.dghjdgf.com/paypal.co.uk/cycgi-bin/webscrcmd=_home-customer&amp;nav=1/loading.php</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>44</v>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>phishing</t>
+        </is>
       </c>
       <c r="E3" t="n">
-        <v>29</v>
+        <v>88</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I3" t="n">
         <v>2</v>
       </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
@@ -1137,133 +1147,133 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>6</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.01136363636363636</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT3" t="n">
         <v>3</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>6</v>
-      </c>
       <c r="AU3" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="AV3" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AW3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX3" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AY3" t="n">
-        <v>9</v>
+        <v>4.375</v>
       </c>
       <c r="AZ3" t="n">
-        <v>6</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>4.416666666666667</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC3" t="n">
         <v>0</v>
@@ -1275,7 +1285,7 @@
         <v>1</v>
       </c>
       <c r="BF3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1355,520 +1365,7 @@
       <c r="CF3" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>www.dghjdgf.com/paypal.co.uk/cycgi-bin/webscrcmd=_home-customer&amp;nav=1/loading.php</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>88</v>
-      </c>
-      <c r="E4" t="n">
-        <v>15</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>5</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0.01136363636363636</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>4.375</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>4.333333333333333</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>4.416666666666667</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>http://192.168.1.1/amazon-login@phishing-secure.com</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>51</v>
-      </c>
-      <c r="E5" t="n">
-        <v>11</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>4</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0.1568627450980392</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0.7272727272727273</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF5" t="n">
+      <c r="CG3" t="n">
         <v>0</v>
       </c>
     </row>

--- a/log_feature_extraction.xlsx
+++ b/log_feature_extraction.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG83"/>
+  <dimension ref="A1:CG113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="34.88671875" customWidth="1" min="2" max="2"/>
@@ -22419,6 +22419,7896 @@
         <v>0</v>
       </c>
       <c r="CG83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>https://www.apple.com</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>21</v>
+      </c>
+      <c r="F84" t="n">
+        <v>13</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" t="n">
+        <v>2</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>2</v>
+      </c>
+      <c r="R84" t="n">
+        <v>0</v>
+      </c>
+      <c r="S84" t="n">
+        <v>1</v>
+      </c>
+      <c r="T84" t="n">
+        <v>0</v>
+      </c>
+      <c r="U84" t="n">
+        <v>0</v>
+      </c>
+      <c r="V84" t="n">
+        <v>0</v>
+      </c>
+      <c r="W84" t="n">
+        <v>0</v>
+      </c>
+      <c r="X84" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ84" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR84" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS84" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT84" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV84" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW84" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY84" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ84" t="n">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="BA84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB84" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC84" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>https://www.google.com</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>22</v>
+      </c>
+      <c r="F85" t="n">
+        <v>14</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" t="n">
+        <v>2</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>2</v>
+      </c>
+      <c r="R85" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" t="n">
+        <v>1</v>
+      </c>
+      <c r="T85" t="n">
+        <v>0</v>
+      </c>
+      <c r="U85" t="n">
+        <v>0</v>
+      </c>
+      <c r="V85" t="n">
+        <v>0</v>
+      </c>
+      <c r="W85" t="n">
+        <v>0</v>
+      </c>
+      <c r="X85" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ85" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR85" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS85" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT85" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV85" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW85" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY85" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AZ85" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>https://smmhejtkx.olghvlbkcdqtscd.top/ksjdbj</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>phishing</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>44</v>
+      </c>
+      <c r="F86" t="n">
+        <v>29</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" t="n">
+        <v>2</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>3</v>
+      </c>
+      <c r="R86" t="n">
+        <v>0</v>
+      </c>
+      <c r="S86" t="n">
+        <v>1</v>
+      </c>
+      <c r="T86" t="n">
+        <v>0</v>
+      </c>
+      <c r="U86" t="n">
+        <v>0</v>
+      </c>
+      <c r="V86" t="n">
+        <v>0</v>
+      </c>
+      <c r="W86" t="n">
+        <v>0</v>
+      </c>
+      <c r="X86" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y86" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z86" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ86" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL86" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ86" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR86" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS86" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT86" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU86" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV86" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW86" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX86" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY86" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ86" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA86" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF86" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG86" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ86" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA86" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB86" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC86" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD86" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE86" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF86" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>https://www.microsoft.com</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>25</v>
+      </c>
+      <c r="F87" t="n">
+        <v>17</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" t="n">
+        <v>2</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>2</v>
+      </c>
+      <c r="R87" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" t="n">
+        <v>1</v>
+      </c>
+      <c r="T87" t="n">
+        <v>0</v>
+      </c>
+      <c r="U87" t="n">
+        <v>0</v>
+      </c>
+      <c r="V87" t="n">
+        <v>0</v>
+      </c>
+      <c r="W87" t="n">
+        <v>0</v>
+      </c>
+      <c r="X87" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y87" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ87" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR87" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS87" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT87" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV87" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW87" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY87" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ87" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB87" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC87" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH87" t="n">
+        <v>102</v>
+      </c>
+      <c r="BI87" t="n">
+        <v>0.5686274509803921</v>
+      </c>
+      <c r="BJ87" t="n">
+        <v>0.4313725490196079</v>
+      </c>
+      <c r="BK87" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP87" t="n">
+        <v>43.61702127659575</v>
+      </c>
+      <c r="BQ87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR87" t="n">
+        <v>100</v>
+      </c>
+      <c r="BS87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU87" t="n">
+        <v>1.96078431372549</v>
+      </c>
+      <c r="BV87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY87" t="n">
+        <v>1</v>
+      </c>
+      <c r="BZ87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>https://www.apple.com</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>21</v>
+      </c>
+      <c r="F88" t="n">
+        <v>13</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" t="n">
+        <v>2</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>2</v>
+      </c>
+      <c r="R88" t="n">
+        <v>0</v>
+      </c>
+      <c r="S88" t="n">
+        <v>1</v>
+      </c>
+      <c r="T88" t="n">
+        <v>0</v>
+      </c>
+      <c r="U88" t="n">
+        <v>0</v>
+      </c>
+      <c r="V88" t="n">
+        <v>0</v>
+      </c>
+      <c r="W88" t="n">
+        <v>0</v>
+      </c>
+      <c r="X88" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y88" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ88" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR88" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS88" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT88" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV88" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW88" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY88" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ88" t="n">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="BA88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB88" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC88" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH88" t="n">
+        <v>139</v>
+      </c>
+      <c r="BI88" t="n">
+        <v>0.7913669064748201</v>
+      </c>
+      <c r="BJ88" t="n">
+        <v>0.2086330935251799</v>
+      </c>
+      <c r="BK88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ88" t="n">
+        <v>64.70588235294117</v>
+      </c>
+      <c r="BR88" t="n">
+        <v>35.29411764705883</v>
+      </c>
+      <c r="BS88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY88" t="n">
+        <v>1</v>
+      </c>
+      <c r="BZ88" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>https://www.google.com</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>22</v>
+      </c>
+      <c r="F89" t="n">
+        <v>14</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" t="n">
+        <v>2</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>2</v>
+      </c>
+      <c r="R89" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" t="n">
+        <v>1</v>
+      </c>
+      <c r="T89" t="n">
+        <v>0</v>
+      </c>
+      <c r="U89" t="n">
+        <v>0</v>
+      </c>
+      <c r="V89" t="n">
+        <v>0</v>
+      </c>
+      <c r="W89" t="n">
+        <v>0</v>
+      </c>
+      <c r="X89" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y89" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ89" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR89" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS89" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT89" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV89" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW89" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY89" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AZ89" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC89" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH89" t="n">
+        <v>12</v>
+      </c>
+      <c r="BI89" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="BJ89" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="BK89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ89" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY89" t="n">
+        <v>1</v>
+      </c>
+      <c r="BZ89" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA89" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB89" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC89" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD89" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE89" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF89" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>https://www.google.com</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>22</v>
+      </c>
+      <c r="F90" t="n">
+        <v>14</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" t="n">
+        <v>2</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>2</v>
+      </c>
+      <c r="R90" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" t="n">
+        <v>1</v>
+      </c>
+      <c r="T90" t="n">
+        <v>0</v>
+      </c>
+      <c r="U90" t="n">
+        <v>0</v>
+      </c>
+      <c r="V90" t="n">
+        <v>0</v>
+      </c>
+      <c r="W90" t="n">
+        <v>0</v>
+      </c>
+      <c r="X90" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y90" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ90" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR90" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS90" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT90" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV90" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW90" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY90" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AZ90" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC90" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH90" t="n">
+        <v>12</v>
+      </c>
+      <c r="BI90" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="BJ90" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="BK90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ90" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY90" t="n">
+        <v>1</v>
+      </c>
+      <c r="BZ90" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA90" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB90" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC90" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD90" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE90" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF90" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>https://www.google.com</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>22</v>
+      </c>
+      <c r="F91" t="n">
+        <v>14</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" t="n">
+        <v>2</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>2</v>
+      </c>
+      <c r="R91" t="n">
+        <v>0</v>
+      </c>
+      <c r="S91" t="n">
+        <v>1</v>
+      </c>
+      <c r="T91" t="n">
+        <v>0</v>
+      </c>
+      <c r="U91" t="n">
+        <v>0</v>
+      </c>
+      <c r="V91" t="n">
+        <v>0</v>
+      </c>
+      <c r="W91" t="n">
+        <v>0</v>
+      </c>
+      <c r="X91" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y91" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ91" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR91" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS91" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT91" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV91" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW91" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY91" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AZ91" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC91" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH91" t="n">
+        <v>12</v>
+      </c>
+      <c r="BI91" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="BJ91" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="BK91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ91" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY91" t="n">
+        <v>1</v>
+      </c>
+      <c r="BZ91" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA91" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB91" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC91" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD91" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE91" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF91" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>https://www.google.com</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>22</v>
+      </c>
+      <c r="F92" t="n">
+        <v>14</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" t="n">
+        <v>2</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>2</v>
+      </c>
+      <c r="R92" t="n">
+        <v>0</v>
+      </c>
+      <c r="S92" t="n">
+        <v>1</v>
+      </c>
+      <c r="T92" t="n">
+        <v>0</v>
+      </c>
+      <c r="U92" t="n">
+        <v>0</v>
+      </c>
+      <c r="V92" t="n">
+        <v>0</v>
+      </c>
+      <c r="W92" t="n">
+        <v>0</v>
+      </c>
+      <c r="X92" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y92" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z92" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ92" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ92" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR92" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS92" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT92" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV92" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW92" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY92" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AZ92" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC92" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH92" t="n">
+        <v>12</v>
+      </c>
+      <c r="BI92" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="BJ92" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="BK92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ92" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY92" t="n">
+        <v>1</v>
+      </c>
+      <c r="BZ92" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>https://github.com</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>18</v>
+      </c>
+      <c r="F93" t="n">
+        <v>10</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" t="n">
+        <v>1</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0</v>
+      </c>
+      <c r="P93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>2</v>
+      </c>
+      <c r="R93" t="n">
+        <v>0</v>
+      </c>
+      <c r="S93" t="n">
+        <v>1</v>
+      </c>
+      <c r="T93" t="n">
+        <v>0</v>
+      </c>
+      <c r="U93" t="n">
+        <v>0</v>
+      </c>
+      <c r="V93" t="n">
+        <v>0</v>
+      </c>
+      <c r="W93" t="n">
+        <v>0</v>
+      </c>
+      <c r="X93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y93" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z93" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ93" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR93" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS93" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT93" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV93" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW93" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY93" t="n">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="AZ93" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA93" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB93" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC93" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD93" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE93" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF93" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG93" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH93" t="n">
+        <v>152</v>
+      </c>
+      <c r="BI93" t="n">
+        <v>0.9144736842105263</v>
+      </c>
+      <c r="BJ93" t="n">
+        <v>0.08552631578947369</v>
+      </c>
+      <c r="BK93" t="n">
+        <v>18</v>
+      </c>
+      <c r="BL93" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM93" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN93" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO93" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP93" t="n">
+        <v>88.78504672897196</v>
+      </c>
+      <c r="BQ93" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR93" t="n">
+        <v>100</v>
+      </c>
+      <c r="BS93" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT93" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU93" t="n">
+        <v>6.578947368421052</v>
+      </c>
+      <c r="BV93" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW93" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX93" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY93" t="n">
+        <v>1</v>
+      </c>
+      <c r="BZ93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>https://www.google.com</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>22</v>
+      </c>
+      <c r="F94" t="n">
+        <v>14</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" t="n">
+        <v>2</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0</v>
+      </c>
+      <c r="P94" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>2</v>
+      </c>
+      <c r="R94" t="n">
+        <v>0</v>
+      </c>
+      <c r="S94" t="n">
+        <v>1</v>
+      </c>
+      <c r="T94" t="n">
+        <v>0</v>
+      </c>
+      <c r="U94" t="n">
+        <v>0</v>
+      </c>
+      <c r="V94" t="n">
+        <v>0</v>
+      </c>
+      <c r="W94" t="n">
+        <v>0</v>
+      </c>
+      <c r="X94" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y94" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ94" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR94" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS94" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT94" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV94" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW94" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY94" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AZ94" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC94" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH94" t="n">
+        <v>12</v>
+      </c>
+      <c r="BI94" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="BJ94" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="BK94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ94" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY94" t="n">
+        <v>1</v>
+      </c>
+      <c r="BZ94" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>https://www.wikipedia.org</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>25</v>
+      </c>
+      <c r="F95" t="n">
+        <v>17</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>2</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0</v>
+      </c>
+      <c r="P95" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>2</v>
+      </c>
+      <c r="R95" t="n">
+        <v>0</v>
+      </c>
+      <c r="S95" t="n">
+        <v>1</v>
+      </c>
+      <c r="T95" t="n">
+        <v>0</v>
+      </c>
+      <c r="U95" t="n">
+        <v>0</v>
+      </c>
+      <c r="V95" t="n">
+        <v>0</v>
+      </c>
+      <c r="W95" t="n">
+        <v>0</v>
+      </c>
+      <c r="X95" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y95" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z95" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ95" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ95" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR95" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS95" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT95" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV95" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW95" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY95" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ95" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH95" t="n">
+        <v>374</v>
+      </c>
+      <c r="BI95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ95" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP95" t="n">
+        <v>42.85714285714285</v>
+      </c>
+      <c r="BQ95" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY95" t="n">
+        <v>1</v>
+      </c>
+      <c r="BZ95" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>https://github.com</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>18</v>
+      </c>
+      <c r="F96" t="n">
+        <v>10</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>1</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0</v>
+      </c>
+      <c r="P96" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>2</v>
+      </c>
+      <c r="R96" t="n">
+        <v>0</v>
+      </c>
+      <c r="S96" t="n">
+        <v>1</v>
+      </c>
+      <c r="T96" t="n">
+        <v>0</v>
+      </c>
+      <c r="U96" t="n">
+        <v>0</v>
+      </c>
+      <c r="V96" t="n">
+        <v>0</v>
+      </c>
+      <c r="W96" t="n">
+        <v>0</v>
+      </c>
+      <c r="X96" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y96" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ96" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR96" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS96" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT96" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV96" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW96" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY96" t="n">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="AZ96" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH96" t="n">
+        <v>152</v>
+      </c>
+      <c r="BI96" t="n">
+        <v>0.9144736842105263</v>
+      </c>
+      <c r="BJ96" t="n">
+        <v>0.08552631578947369</v>
+      </c>
+      <c r="BK96" t="n">
+        <v>18</v>
+      </c>
+      <c r="BL96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP96" t="n">
+        <v>88.78504672897196</v>
+      </c>
+      <c r="BQ96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR96" t="n">
+        <v>100</v>
+      </c>
+      <c r="BS96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU96" t="n">
+        <v>6.578947368421052</v>
+      </c>
+      <c r="BV96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BZ96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>https://www.microsoft.com</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>25</v>
+      </c>
+      <c r="F97" t="n">
+        <v>17</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>2</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0</v>
+      </c>
+      <c r="P97" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>2</v>
+      </c>
+      <c r="R97" t="n">
+        <v>0</v>
+      </c>
+      <c r="S97" t="n">
+        <v>1</v>
+      </c>
+      <c r="T97" t="n">
+        <v>0</v>
+      </c>
+      <c r="U97" t="n">
+        <v>0</v>
+      </c>
+      <c r="V97" t="n">
+        <v>0</v>
+      </c>
+      <c r="W97" t="n">
+        <v>0</v>
+      </c>
+      <c r="X97" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y97" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z97" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ97" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM97" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ97" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR97" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS97" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT97" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV97" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW97" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY97" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ97" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB97" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC97" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>https://www.google.com</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>22</v>
+      </c>
+      <c r="F98" t="n">
+        <v>14</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" t="n">
+        <v>2</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0</v>
+      </c>
+      <c r="P98" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>2</v>
+      </c>
+      <c r="R98" t="n">
+        <v>0</v>
+      </c>
+      <c r="S98" t="n">
+        <v>1</v>
+      </c>
+      <c r="T98" t="n">
+        <v>0</v>
+      </c>
+      <c r="U98" t="n">
+        <v>0</v>
+      </c>
+      <c r="V98" t="n">
+        <v>0</v>
+      </c>
+      <c r="W98" t="n">
+        <v>0</v>
+      </c>
+      <c r="X98" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y98" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ98" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR98" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS98" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT98" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV98" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW98" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY98" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AZ98" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC98" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH98" t="n">
+        <v>12</v>
+      </c>
+      <c r="BI98" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="BJ98" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="BK98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ98" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY98" t="n">
+        <v>1</v>
+      </c>
+      <c r="BZ98" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>https://www.google.com</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>22</v>
+      </c>
+      <c r="F99" t="n">
+        <v>14</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" t="n">
+        <v>2</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>2</v>
+      </c>
+      <c r="R99" t="n">
+        <v>0</v>
+      </c>
+      <c r="S99" t="n">
+        <v>1</v>
+      </c>
+      <c r="T99" t="n">
+        <v>0</v>
+      </c>
+      <c r="U99" t="n">
+        <v>0</v>
+      </c>
+      <c r="V99" t="n">
+        <v>0</v>
+      </c>
+      <c r="W99" t="n">
+        <v>0</v>
+      </c>
+      <c r="X99" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y99" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z99" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ99" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ99" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR99" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS99" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT99" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV99" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW99" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY99" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AZ99" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC99" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH99" t="n">
+        <v>12</v>
+      </c>
+      <c r="BI99" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="BJ99" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="BK99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ99" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY99" t="n">
+        <v>1</v>
+      </c>
+      <c r="BZ99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>https://github.com</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>18</v>
+      </c>
+      <c r="F100" t="n">
+        <v>10</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" t="n">
+        <v>1</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0</v>
+      </c>
+      <c r="P100" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>2</v>
+      </c>
+      <c r="R100" t="n">
+        <v>0</v>
+      </c>
+      <c r="S100" t="n">
+        <v>1</v>
+      </c>
+      <c r="T100" t="n">
+        <v>0</v>
+      </c>
+      <c r="U100" t="n">
+        <v>0</v>
+      </c>
+      <c r="V100" t="n">
+        <v>0</v>
+      </c>
+      <c r="W100" t="n">
+        <v>0</v>
+      </c>
+      <c r="X100" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y100" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z100" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ100" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR100" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS100" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT100" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV100" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW100" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY100" t="n">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="AZ100" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC100" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH100" t="n">
+        <v>152</v>
+      </c>
+      <c r="BI100" t="n">
+        <v>0.9144736842105263</v>
+      </c>
+      <c r="BJ100" t="n">
+        <v>0.08552631578947369</v>
+      </c>
+      <c r="BK100" t="n">
+        <v>18</v>
+      </c>
+      <c r="BL100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO100" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP100" t="n">
+        <v>88.78504672897196</v>
+      </c>
+      <c r="BQ100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR100" t="n">
+        <v>100</v>
+      </c>
+      <c r="BS100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU100" t="n">
+        <v>6.578947368421052</v>
+      </c>
+      <c r="BV100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY100" t="n">
+        <v>1</v>
+      </c>
+      <c r="BZ100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>https://www.google.com</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>22</v>
+      </c>
+      <c r="F101" t="n">
+        <v>14</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" t="n">
+        <v>2</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0</v>
+      </c>
+      <c r="P101" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>2</v>
+      </c>
+      <c r="R101" t="n">
+        <v>0</v>
+      </c>
+      <c r="S101" t="n">
+        <v>1</v>
+      </c>
+      <c r="T101" t="n">
+        <v>0</v>
+      </c>
+      <c r="U101" t="n">
+        <v>0</v>
+      </c>
+      <c r="V101" t="n">
+        <v>0</v>
+      </c>
+      <c r="W101" t="n">
+        <v>0</v>
+      </c>
+      <c r="X101" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y101" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ101" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR101" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS101" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT101" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV101" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW101" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY101" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AZ101" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC101" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH101" t="n">
+        <v>12</v>
+      </c>
+      <c r="BI101" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="BJ101" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="BK101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ101" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY101" t="n">
+        <v>1</v>
+      </c>
+      <c r="BZ101" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>https://www.google.com</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>22</v>
+      </c>
+      <c r="F102" t="n">
+        <v>14</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" t="n">
+        <v>2</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0</v>
+      </c>
+      <c r="P102" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>2</v>
+      </c>
+      <c r="R102" t="n">
+        <v>0</v>
+      </c>
+      <c r="S102" t="n">
+        <v>1</v>
+      </c>
+      <c r="T102" t="n">
+        <v>0</v>
+      </c>
+      <c r="U102" t="n">
+        <v>0</v>
+      </c>
+      <c r="V102" t="n">
+        <v>0</v>
+      </c>
+      <c r="W102" t="n">
+        <v>0</v>
+      </c>
+      <c r="X102" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y102" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z102" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ102" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ102" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR102" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS102" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT102" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV102" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW102" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY102" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AZ102" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC102" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH102" t="n">
+        <v>12</v>
+      </c>
+      <c r="BI102" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="BJ102" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="BK102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ102" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY102" t="n">
+        <v>1</v>
+      </c>
+      <c r="BZ102" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>https://github.com</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>18</v>
+      </c>
+      <c r="F103" t="n">
+        <v>10</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" t="n">
+        <v>1</v>
+      </c>
+      <c r="I103" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0</v>
+      </c>
+      <c r="P103" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>2</v>
+      </c>
+      <c r="R103" t="n">
+        <v>0</v>
+      </c>
+      <c r="S103" t="n">
+        <v>1</v>
+      </c>
+      <c r="T103" t="n">
+        <v>0</v>
+      </c>
+      <c r="U103" t="n">
+        <v>0</v>
+      </c>
+      <c r="V103" t="n">
+        <v>0</v>
+      </c>
+      <c r="W103" t="n">
+        <v>0</v>
+      </c>
+      <c r="X103" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y103" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z103" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ103" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR103" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS103" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT103" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV103" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW103" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY103" t="n">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="AZ103" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC103" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH103" t="n">
+        <v>152</v>
+      </c>
+      <c r="BI103" t="n">
+        <v>0.9144736842105263</v>
+      </c>
+      <c r="BJ103" t="n">
+        <v>0.08552631578947369</v>
+      </c>
+      <c r="BK103" t="n">
+        <v>18</v>
+      </c>
+      <c r="BL103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO103" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP103" t="n">
+        <v>88.78504672897196</v>
+      </c>
+      <c r="BQ103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR103" t="n">
+        <v>100</v>
+      </c>
+      <c r="BS103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU103" t="n">
+        <v>6.578947368421052</v>
+      </c>
+      <c r="BV103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY103" t="n">
+        <v>1</v>
+      </c>
+      <c r="BZ103" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>https://www.google.com</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>22</v>
+      </c>
+      <c r="F104" t="n">
+        <v>14</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" t="n">
+        <v>2</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" t="n">
+        <v>0</v>
+      </c>
+      <c r="P104" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>2</v>
+      </c>
+      <c r="R104" t="n">
+        <v>0</v>
+      </c>
+      <c r="S104" t="n">
+        <v>1</v>
+      </c>
+      <c r="T104" t="n">
+        <v>0</v>
+      </c>
+      <c r="U104" t="n">
+        <v>0</v>
+      </c>
+      <c r="V104" t="n">
+        <v>0</v>
+      </c>
+      <c r="W104" t="n">
+        <v>0</v>
+      </c>
+      <c r="X104" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y104" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z104" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ104" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ104" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR104" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS104" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT104" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV104" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW104" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY104" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AZ104" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC104" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH104" t="n">
+        <v>12</v>
+      </c>
+      <c r="BI104" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="BJ104" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="BK104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ104" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY104" t="n">
+        <v>1</v>
+      </c>
+      <c r="BZ104" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>www.dghjdgf.com/paypal.co.uk/cycgi-bin/webscrcmd=_home-customer&amp;nav=1/loading.php</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>phishing</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>88</v>
+      </c>
+      <c r="F105" t="n">
+        <v>15</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" t="n">
+        <v>5</v>
+      </c>
+      <c r="I105" t="n">
+        <v>2</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" t="n">
+        <v>1</v>
+      </c>
+      <c r="M105" t="n">
+        <v>2</v>
+      </c>
+      <c r="N105" t="n">
+        <v>1</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0</v>
+      </c>
+      <c r="P105" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>6</v>
+      </c>
+      <c r="R105" t="n">
+        <v>0</v>
+      </c>
+      <c r="S105" t="n">
+        <v>1</v>
+      </c>
+      <c r="T105" t="n">
+        <v>0</v>
+      </c>
+      <c r="U105" t="n">
+        <v>0</v>
+      </c>
+      <c r="V105" t="n">
+        <v>0</v>
+      </c>
+      <c r="W105" t="n">
+        <v>0</v>
+      </c>
+      <c r="X105" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y105" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z105" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC105" t="n">
+        <v>0.01136363636363636</v>
+      </c>
+      <c r="AD105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ105" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN105" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ105" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR105" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS105" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT105" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU105" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV105" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW105" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX105" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY105" t="n">
+        <v>4.375</v>
+      </c>
+      <c r="AZ105" t="n">
+        <v>4.333333333333333</v>
+      </c>
+      <c r="BA105" t="n">
+        <v>4.416666666666667</v>
+      </c>
+      <c r="BB105" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE105" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>https://www.google.com</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>22</v>
+      </c>
+      <c r="F106" t="n">
+        <v>14</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" t="n">
+        <v>2</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0</v>
+      </c>
+      <c r="P106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>2</v>
+      </c>
+      <c r="R106" t="n">
+        <v>0</v>
+      </c>
+      <c r="S106" t="n">
+        <v>1</v>
+      </c>
+      <c r="T106" t="n">
+        <v>0</v>
+      </c>
+      <c r="U106" t="n">
+        <v>0</v>
+      </c>
+      <c r="V106" t="n">
+        <v>0</v>
+      </c>
+      <c r="W106" t="n">
+        <v>0</v>
+      </c>
+      <c r="X106" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y106" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z106" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ106" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ106" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR106" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS106" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT106" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV106" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW106" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY106" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AZ106" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC106" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH106" t="n">
+        <v>12</v>
+      </c>
+      <c r="BI106" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="BJ106" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="BK106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ106" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY106" t="n">
+        <v>1</v>
+      </c>
+      <c r="BZ106" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>https://github.com</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>18</v>
+      </c>
+      <c r="F107" t="n">
+        <v>10</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" t="n">
+        <v>1</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0</v>
+      </c>
+      <c r="P107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>2</v>
+      </c>
+      <c r="R107" t="n">
+        <v>0</v>
+      </c>
+      <c r="S107" t="n">
+        <v>1</v>
+      </c>
+      <c r="T107" t="n">
+        <v>0</v>
+      </c>
+      <c r="U107" t="n">
+        <v>0</v>
+      </c>
+      <c r="V107" t="n">
+        <v>0</v>
+      </c>
+      <c r="W107" t="n">
+        <v>0</v>
+      </c>
+      <c r="X107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y107" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z107" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ107" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR107" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS107" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT107" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV107" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW107" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY107" t="n">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="AZ107" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC107" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH107" t="n">
+        <v>152</v>
+      </c>
+      <c r="BI107" t="n">
+        <v>0.9144736842105263</v>
+      </c>
+      <c r="BJ107" t="n">
+        <v>0.08552631578947369</v>
+      </c>
+      <c r="BK107" t="n">
+        <v>18</v>
+      </c>
+      <c r="BL107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO107" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP107" t="n">
+        <v>88.78504672897196</v>
+      </c>
+      <c r="BQ107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR107" t="n">
+        <v>100</v>
+      </c>
+      <c r="BS107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU107" t="n">
+        <v>6.578947368421052</v>
+      </c>
+      <c r="BV107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY107" t="n">
+        <v>1</v>
+      </c>
+      <c r="BZ107" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>https://www.google.com</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>22</v>
+      </c>
+      <c r="F108" t="n">
+        <v>14</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" t="n">
+        <v>2</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" t="n">
+        <v>0</v>
+      </c>
+      <c r="N108" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" t="n">
+        <v>0</v>
+      </c>
+      <c r="P108" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>2</v>
+      </c>
+      <c r="R108" t="n">
+        <v>0</v>
+      </c>
+      <c r="S108" t="n">
+        <v>1</v>
+      </c>
+      <c r="T108" t="n">
+        <v>0</v>
+      </c>
+      <c r="U108" t="n">
+        <v>0</v>
+      </c>
+      <c r="V108" t="n">
+        <v>0</v>
+      </c>
+      <c r="W108" t="n">
+        <v>0</v>
+      </c>
+      <c r="X108" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y108" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z108" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ108" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ108" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR108" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS108" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT108" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV108" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW108" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY108" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AZ108" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC108" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH108" t="n">
+        <v>12</v>
+      </c>
+      <c r="BI108" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="BJ108" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="BK108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ108" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY108" t="n">
+        <v>1</v>
+      </c>
+      <c r="BZ108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>https://www.google.com</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>22</v>
+      </c>
+      <c r="F109" t="n">
+        <v>14</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" t="n">
+        <v>2</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" t="n">
+        <v>0</v>
+      </c>
+      <c r="N109" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0</v>
+      </c>
+      <c r="P109" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>2</v>
+      </c>
+      <c r="R109" t="n">
+        <v>0</v>
+      </c>
+      <c r="S109" t="n">
+        <v>1</v>
+      </c>
+      <c r="T109" t="n">
+        <v>0</v>
+      </c>
+      <c r="U109" t="n">
+        <v>0</v>
+      </c>
+      <c r="V109" t="n">
+        <v>0</v>
+      </c>
+      <c r="W109" t="n">
+        <v>0</v>
+      </c>
+      <c r="X109" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y109" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ109" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR109" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS109" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT109" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV109" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW109" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY109" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AZ109" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH109" t="n">
+        <v>12</v>
+      </c>
+      <c r="BI109" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="BJ109" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="BK109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ109" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BZ109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>https://github.com</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>18</v>
+      </c>
+      <c r="F110" t="n">
+        <v>10</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I110" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" t="n">
+        <v>0</v>
+      </c>
+      <c r="N110" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" t="n">
+        <v>0</v>
+      </c>
+      <c r="P110" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>2</v>
+      </c>
+      <c r="R110" t="n">
+        <v>0</v>
+      </c>
+      <c r="S110" t="n">
+        <v>1</v>
+      </c>
+      <c r="T110" t="n">
+        <v>0</v>
+      </c>
+      <c r="U110" t="n">
+        <v>0</v>
+      </c>
+      <c r="V110" t="n">
+        <v>0</v>
+      </c>
+      <c r="W110" t="n">
+        <v>0</v>
+      </c>
+      <c r="X110" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y110" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ110" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR110" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS110" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT110" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV110" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW110" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY110" t="n">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="AZ110" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH110" t="n">
+        <v>152</v>
+      </c>
+      <c r="BI110" t="n">
+        <v>0.9144736842105263</v>
+      </c>
+      <c r="BJ110" t="n">
+        <v>0.08552631578947369</v>
+      </c>
+      <c r="BK110" t="n">
+        <v>18</v>
+      </c>
+      <c r="BL110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP110" t="n">
+        <v>88.78504672897196</v>
+      </c>
+      <c r="BQ110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR110" t="n">
+        <v>100</v>
+      </c>
+      <c r="BS110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU110" t="n">
+        <v>6.578947368421052</v>
+      </c>
+      <c r="BV110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BZ110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>https://www.google.com</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>22</v>
+      </c>
+      <c r="F111" t="n">
+        <v>14</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" t="n">
+        <v>2</v>
+      </c>
+      <c r="I111" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" t="n">
+        <v>0</v>
+      </c>
+      <c r="K111" t="n">
+        <v>0</v>
+      </c>
+      <c r="L111" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" t="n">
+        <v>0</v>
+      </c>
+      <c r="N111" t="n">
+        <v>0</v>
+      </c>
+      <c r="O111" t="n">
+        <v>0</v>
+      </c>
+      <c r="P111" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>2</v>
+      </c>
+      <c r="R111" t="n">
+        <v>0</v>
+      </c>
+      <c r="S111" t="n">
+        <v>1</v>
+      </c>
+      <c r="T111" t="n">
+        <v>0</v>
+      </c>
+      <c r="U111" t="n">
+        <v>0</v>
+      </c>
+      <c r="V111" t="n">
+        <v>0</v>
+      </c>
+      <c r="W111" t="n">
+        <v>0</v>
+      </c>
+      <c r="X111" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y111" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z111" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ111" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ111" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR111" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS111" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT111" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV111" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW111" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY111" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AZ111" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA111" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB111" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC111" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD111" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE111" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF111" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG111" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH111" t="n">
+        <v>12</v>
+      </c>
+      <c r="BI111" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="BJ111" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="BK111" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL111" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM111" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN111" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO111" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP111" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ111" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR111" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS111" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT111" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU111" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV111" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW111" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX111" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY111" t="n">
+        <v>1</v>
+      </c>
+      <c r="BZ111" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>https://www.microsoft.com</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>25</v>
+      </c>
+      <c r="F112" t="n">
+        <v>17</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" t="n">
+        <v>2</v>
+      </c>
+      <c r="I112" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" t="n">
+        <v>0</v>
+      </c>
+      <c r="L112" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" t="n">
+        <v>0</v>
+      </c>
+      <c r="N112" t="n">
+        <v>0</v>
+      </c>
+      <c r="O112" t="n">
+        <v>0</v>
+      </c>
+      <c r="P112" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>2</v>
+      </c>
+      <c r="R112" t="n">
+        <v>0</v>
+      </c>
+      <c r="S112" t="n">
+        <v>1</v>
+      </c>
+      <c r="T112" t="n">
+        <v>0</v>
+      </c>
+      <c r="U112" t="n">
+        <v>0</v>
+      </c>
+      <c r="V112" t="n">
+        <v>0</v>
+      </c>
+      <c r="W112" t="n">
+        <v>0</v>
+      </c>
+      <c r="X112" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y112" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ112" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR112" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS112" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT112" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV112" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW112" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY112" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ112" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB112" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC112" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH112" t="n">
+        <v>102</v>
+      </c>
+      <c r="BI112" t="n">
+        <v>0.5686274509803921</v>
+      </c>
+      <c r="BJ112" t="n">
+        <v>0.4313725490196079</v>
+      </c>
+      <c r="BK112" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP112" t="n">
+        <v>43.61702127659575</v>
+      </c>
+      <c r="BQ112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR112" t="n">
+        <v>100</v>
+      </c>
+      <c r="BS112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU112" t="n">
+        <v>1.96078431372549</v>
+      </c>
+      <c r="BV112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY112" t="n">
+        <v>1</v>
+      </c>
+      <c r="BZ112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>https://github.com</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>18</v>
+      </c>
+      <c r="F113" t="n">
+        <v>10</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" t="n">
+        <v>1</v>
+      </c>
+      <c r="I113" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" t="n">
+        <v>0</v>
+      </c>
+      <c r="N113" t="n">
+        <v>0</v>
+      </c>
+      <c r="O113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P113" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>2</v>
+      </c>
+      <c r="R113" t="n">
+        <v>0</v>
+      </c>
+      <c r="S113" t="n">
+        <v>1</v>
+      </c>
+      <c r="T113" t="n">
+        <v>0</v>
+      </c>
+      <c r="U113" t="n">
+        <v>0</v>
+      </c>
+      <c r="V113" t="n">
+        <v>0</v>
+      </c>
+      <c r="W113" t="n">
+        <v>0</v>
+      </c>
+      <c r="X113" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y113" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z113" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ113" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR113" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS113" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT113" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV113" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW113" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY113" t="n">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="AZ113" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC113" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH113" t="n">
+        <v>152</v>
+      </c>
+      <c r="BI113" t="n">
+        <v>0.9144736842105263</v>
+      </c>
+      <c r="BJ113" t="n">
+        <v>0.08552631578947369</v>
+      </c>
+      <c r="BK113" t="n">
+        <v>18</v>
+      </c>
+      <c r="BL113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO113" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP113" t="n">
+        <v>88.78504672897196</v>
+      </c>
+      <c r="BQ113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR113" t="n">
+        <v>100</v>
+      </c>
+      <c r="BS113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU113" t="n">
+        <v>6.578947368421052</v>
+      </c>
+      <c r="BV113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY113" t="n">
+        <v>1</v>
+      </c>
+      <c r="BZ113" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG113" t="n">
         <v>0</v>
       </c>
     </row>

--- a/log_feature_extraction.xlsx
+++ b/log_feature_extraction.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG113"/>
+  <dimension ref="A1:CG115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="34.88671875" customWidth="1" min="2" max="2"/>
@@ -30309,6 +30309,532 @@
         <v>0</v>
       </c>
       <c r="CG113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>https://www.google.com</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>22</v>
+      </c>
+      <c r="F114" t="n">
+        <v>14</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" t="n">
+        <v>2</v>
+      </c>
+      <c r="I114" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0</v>
+      </c>
+      <c r="K114" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" t="n">
+        <v>0</v>
+      </c>
+      <c r="N114" t="n">
+        <v>0</v>
+      </c>
+      <c r="O114" t="n">
+        <v>0</v>
+      </c>
+      <c r="P114" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>2</v>
+      </c>
+      <c r="R114" t="n">
+        <v>0</v>
+      </c>
+      <c r="S114" t="n">
+        <v>1</v>
+      </c>
+      <c r="T114" t="n">
+        <v>0</v>
+      </c>
+      <c r="U114" t="n">
+        <v>0</v>
+      </c>
+      <c r="V114" t="n">
+        <v>0</v>
+      </c>
+      <c r="W114" t="n">
+        <v>0</v>
+      </c>
+      <c r="X114" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y114" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z114" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ114" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ114" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR114" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS114" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT114" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV114" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW114" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY114" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AZ114" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC114" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH114" t="n">
+        <v>12</v>
+      </c>
+      <c r="BI114" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="BJ114" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="BK114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ114" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY114" t="n">
+        <v>1</v>
+      </c>
+      <c r="BZ114" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>https://www.google.com</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>22</v>
+      </c>
+      <c r="F115" t="n">
+        <v>14</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" t="n">
+        <v>2</v>
+      </c>
+      <c r="I115" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" t="n">
+        <v>0</v>
+      </c>
+      <c r="N115" t="n">
+        <v>0</v>
+      </c>
+      <c r="O115" t="n">
+        <v>0</v>
+      </c>
+      <c r="P115" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>2</v>
+      </c>
+      <c r="R115" t="n">
+        <v>0</v>
+      </c>
+      <c r="S115" t="n">
+        <v>1</v>
+      </c>
+      <c r="T115" t="n">
+        <v>0</v>
+      </c>
+      <c r="U115" t="n">
+        <v>0</v>
+      </c>
+      <c r="V115" t="n">
+        <v>0</v>
+      </c>
+      <c r="W115" t="n">
+        <v>0</v>
+      </c>
+      <c r="X115" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y115" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ115" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR115" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS115" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT115" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV115" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW115" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY115" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AZ115" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC115" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH115" t="n">
+        <v>12</v>
+      </c>
+      <c r="BI115" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="BJ115" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="BK115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ115" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY115" t="n">
+        <v>1</v>
+      </c>
+      <c r="BZ115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG115" t="n">
         <v>0</v>
       </c>
     </row>

--- a/log_feature_extraction.xlsx
+++ b/log_feature_extraction.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI17"/>
+  <dimension ref="A1:CI18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -5274,6 +5274,282 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>https://www.google.com</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>22</v>
+      </c>
+      <c r="F18" t="n">
+        <v>14</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>12</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH18" t="inlineStr">
+        <is>
+          <t>🟢 URL terdeteksi sebagai BENIGN dengan phishing probability 33.38% (BENIGN Range: 0.00-0.60). Benign Confidence: 66.62%. Top features: length_words_raw (0.052), char_repeat (0.052), length_url (0.024), length_hostname (0.024), web_traffic (0.019). Website ini AMAN untuk dikunjungi.</t>
+        </is>
+      </c>
+      <c r="CI18" t="inlineStr">
+        <is>
+          <t>1. length_words_raw | NEUTRAL | Tidak ada dampak signifikan (0.0518)
+2. char_repeat | NEUTRAL | Tidak ada dampak signifikan (0.0518)
+3. length_url | NEUTRAL | Tidak ada dampak signifikan (0.0239)
+4. length_hostname | NEUTRAL | Tidak ada dampak signifikan (0.0239)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/log_feature_extraction.xlsx
+++ b/log_feature_extraction.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CJ16"/>
+  <dimension ref="A1:CJ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="3.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5239,6 +5239,866 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>https://www.google.com</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>22</v>
+      </c>
+      <c r="F17" t="n">
+        <v>14</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>12</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH17" t="inlineStr">
+        <is>
+          <t>🟢 URL terdeteksi sebagai BENIGN dengan phishing probability 33.38% (BENIGN Range: 0.00-0.60). Benign Confidence: 66.62%. Top features: length_words_raw (0.052), char_repeat (0.052), length_url (0.024), length_hostname (0.024), web_traffic (0.019). Website ini AMAN untuk dikunjungi.</t>
+        </is>
+      </c>
+      <c r="CI17" t="inlineStr">
+        <is>
+          <t>1. length_words_raw | NEUTRAL | Tidak ada dampak signifikan (0.0518)
+2. char_repeat | NEUTRAL | Tidak ada dampak signifikan (0.0518)
+3. length_url | NEUTRAL | Tidak ada dampak signifikan (0.0239)
+4. length_hostname | NEUTRAL | Tidak ada dampak signifikan (0.0239)</t>
+        </is>
+      </c>
+      <c r="CJ17" t="inlineStr">
+        <is>
+          <t>URL "https://www.google.com" diklasifikasikan sebagai "benign" karena beberapa alasan:
+1. **Domain nama yang terdaftar**: "google.com" adalah domain nama yang terdaftar dan sah, milik perusahaan Google LLC. Domain nama yang terdaftar menunjukkan bahwa situs web tersebut telah mengikuti proses registrasi yang valid dan sah.
+2. **Konteks URL yang jelas**: URL tersebut memiliki struktur yang jelas dan membedakan antara kata-kata yang berbeda. Hal ini membuat URL tersebut memiliki konteks yang jelas dan tidak berisiko.
+3. **Ditindaklanjuti oleh peramban web**: Peramban web dapat dengan mudah mengeksekusi URL tersebut dan menampilkan halaman di Google. Hal ini menunjukkan bahwa URL tersebut dapat dialamatkan dengan benar dan tidak memiliki masalah teknis.
+4. **Tidak mengandung kata-kata ambigu**: URL tersebut tidak mengandung kata-kata yang ambigu atau mencurigakan, seperti kata-kata yang terkait dengan malware, phishing, atau penipuan.
+5. **Tidak memiliki ekstensi yang mencurigakan**: URL tersebut tidak memiliki ekstensi yang mencurigakan, seperti ".exe" atau ".zip", yang dapat menunjukkan bahwa file tersebut berisi malware.
+Dengan demikian, URL "https://www.google.com" diklasifikasikan sebagai "benign" karena memiliki domain nama yang terdaftar, konteks URL yang jelas, dapat ditindaklanjuti oleh peramban web, tidak mengandung kata-kata ambigu, dan tidak memiliki ekstensi yang mencurigakan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>https://www.microsoft.com</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>25</v>
+      </c>
+      <c r="F18" t="n">
+        <v>17</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>101</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>0.5643564356435643</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>0.4356435643564356</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>43.61702127659575</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>100</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>1.98019801980198</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH18" t="inlineStr">
+        <is>
+          <t>🟢 URL terdeteksi sebagai BENIGN dengan phishing probability 9.91% (BENIGN Range: 0.00-0.60). Benign Confidence: 90.09%. Top features: length_words_raw (0.047), char_repeat (0.047), length_hostname (0.026), length_url (0.026), google_index (0.019). Website ini AMAN untuk dikunjungi.</t>
+        </is>
+      </c>
+      <c r="CI18" t="inlineStr">
+        <is>
+          <t>1. length_words_raw | NEUTRAL | Tidak ada dampak signifikan (0.0466)
+2. char_repeat | NEUTRAL | Tidak ada dampak signifikan (0.0466)
+3. length_hostname | NEUTRAL | Tidak ada dampak signifikan (0.0256)
+4. length_url | NEUTRAL | Tidak ada dampak signifikan (0.0256)</t>
+        </is>
+      </c>
+      <c r="CJ18" t="inlineStr">
+        <is>
+          <t>URL tersebut diklasifikasikan sebagai benign karena beberapa alasan:
+1. **Dikenal secara umum**: Microsoft adalah sebuah perusahaan teknologi yang terkenal dan diakui secara global. Nama domain (`www.microsoft.com`) juga terlihat jelas dan tidak mengandung kata-kata yang mencurigakan.
+2. **Konteks web yang jelas**: URL tersebut mengarah ke situs web resmi dari Microsoft, yang menawarkan berbagai informasi dan layanan yang sah, seperti unduhan software, dukungan teknis, dan lain-lain.
+3. **Situs web yang aman**: Microsoft memiliki reputasi yang baik dalam hal keamanan dan privasi, sehingga situs webnya juga dianggap aman untuk diakses.
+4. **Tidak ada kata-kata mencurigakan**: URL tersebut tidak mengandung kata-kata yang mencurigakan atau berbahaya, seperti `malware` , `virus`, `sploit`, atau `phishing`.
+Dengan demikian, URL tersebut diklasifikasikan sebagai benign karena tidak memiliki ciri-ciri yang mencurigakan atau berbahaya.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>http://paypal-verify-account-urgent.suspicious.tk</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>phishing</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>49</v>
+      </c>
+      <c r="F19" t="n">
+        <v>42</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>5.857142857142857</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>6.166666666666667</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH19" t="inlineStr">
+        <is>
+          <t>🔴 URL terdeteksi sebagai PHISHING dengan phishing probability 10.00% (PHISHING Range: 0.60-1.00). 1 fitur utama menunjukkan indikator phishing berbahaya. Website ini TIDAK AMAN untuk dikunjungi.</t>
+        </is>
+      </c>
+      <c r="CI19" t="inlineStr">
+        <is>
+          <t>1. ip | BENIGN | ip = 0 (tidak ada indikator phishing) ()
+2. nb_at | BENIGN | nb_at = 0 (tidak ada indikator phishing) ()
+3. suspicious_tld | PHISHING | TLD mencurigakan ()
+4. random_domain | BENIGN | random_domain = 0 (tidak ada indikator phishing) ()
+5. shortening_service | BENIGN | shortening_service = 0 (tidak ada indikator phishing) ()</t>
+        </is>
+      </c>
+      <c r="CJ19" t="inlineStr">
+        <is>
+          <t>URL tersebut diklasifikasikan sebagai phishing karena beberapa alasan:
+1. **Niat yang tidak jelas**: URL tersebut berisi kata-kata seperti "verify-account-urgent" yang menunjukkan bahwa alamat tersebut ingin meminta pengguna untuk melakukan verifikasi akun secara mendadak. Hal ini dapat membuat pengguna merasa khawatir dan langsung masuk ke dalam website tersebut, sehingga tidak memeriksa keasliannya.
+2. **Domain yang tidak jelas**: URL tersebut menggunakan domain ".suspicious.tk" yang tidak familiar. Domain yang tidak jelas atau bahkan yang dianggap "suspicious" dapat menunjukkan bahwa alamat tersebut tidak dapat dipercaya.
+3. **Kata-kata yang menakutkan**: Kata-kata seperti "urgent" dan "verify-account" dapat membuat pengguna merasa khawatir dan langsung melakukan aksi tanpa memeriksa keaslian alamat tersebut.
+4. **Keterlibatan merek yang terkenal**: URL tersebut menggunakan nama "paypal", yaitu sebuah platform pembayaran online yang terkenal. Phishing seringkali menggunakan nama merek yang terkenal untuk menipu pengguna. Dengan menggunakan nama merek yang terkenal, phishing dapat membuat pengguna percaya bahwa alamat tersebut adalah asli dan dapat dipercaya.
+Dengan demikian, URL tersebut dapat diklasifikasikan sebagai phishing karena memiliki beberapa ciri-ciri yang mencurigakan dan dapat menipu pengguna.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId1"/>

--- a/log_feature_extraction.xlsx
+++ b/log_feature_extraction.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CJ19"/>
+  <dimension ref="A1:CJ45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="3.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -6099,6 +6099,7464 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>https://www.wikipedia.org</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>25</v>
+      </c>
+      <c r="F20" t="n">
+        <v>17</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>376</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>0.005319148936170213</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>0.9946808510638298</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>42.85714285714285</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>0.5319148936170213</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>1</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH20" t="inlineStr">
+        <is>
+          <t>🟢 URL terdeteksi sebagai BENIGN dengan phishing probability 5.05% (BENIGN Range: 0.00-0.60). Benign Confidence: 94.95%. Top features: char_repeat (0.056), length_words_raw (0.056), length_url (0.024), length_hostname (0.024), google_index (0.019). Website ini AMAN untuk dikunjungi.</t>
+        </is>
+      </c>
+      <c r="CI20" t="inlineStr">
+        <is>
+          <t>1. char_repeat | NEUTRAL | Tidak ada dampak signifikan (0.0562)
+2. length_words_raw | NEUTRAL | Tidak ada dampak signifikan (0.0562)
+3. length_url | NEUTRAL | Tidak ada dampak signifikan (0.0244)
+4. length_hostname | NEUTRAL | Tidak ada dampak signifikan (0.0244)</t>
+        </is>
+      </c>
+      <c r="CJ20" t="inlineStr">
+        <is>
+          <t>URL https://www.wikipedia.org diklasifikasikan sebagai benign karena beberapa alasan:
+1. **Domain yang dapat diandalkan**: Domain wikipedia.org adalah situs web yang sangat terkemuka dan dapat diandalkan, yang merupakan organisasi nirlaba yang menyediakan informasi bebas dan akurat.
+2. **Kegunaan yang jelas**: Situs web ini memiliki kegunaan yang jelas, yaitu menyediakan informasi tentang berbagai topik, termasuk sejarah, sains, politik, dan lain-lain. Kegunaan ini tidak mencurigakan atau memiliki tujuan yang tidak jelas.
+3. **Penggunaan HTTPS**: URL ini menggunakan HTTPS (Hypertext Transfer Protocol Secure), yang berarti bahwa data yang dikirimkan antara pengguna dan server situs web dienkripsi, sehingga memberi perlindungan dari kebocoran data.
+4. **Keterlibatan organisasi**: Wikipedia adalah organisasi yang terkemuka dan terbuka, dengan komunitas editor yang luas dan beragam. Keterlibatan organisasi ini memberi jaminan bahwa konten yang disediakan adalah akurat dan dapat diandalkan.
+Dengan demikian, URL https://www.wikipedia.org diklasifikasikan sebagai benign karena memiliki kegunaan yang jelas, domain yang dapat diandalkan, penggunaan HTTPS, dan keterlibatan organisasi yang terkemuka.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>https://www.google.com</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>22</v>
+      </c>
+      <c r="F21" t="n">
+        <v>14</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>12</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY21" t="n">
+        <v>1</v>
+      </c>
+      <c r="BZ21" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH21" t="inlineStr">
+        <is>
+          <t>🟢 URL terdeteksi sebagai BENIGN dengan phishing probability 33.38% (BENIGN Range: 0.00-0.60). Benign Confidence: 66.62%. Top features: length_words_raw (0.052), char_repeat (0.052), length_url (0.024), length_hostname (0.024), web_traffic (0.019). Website ini AMAN untuk dikunjungi.</t>
+        </is>
+      </c>
+      <c r="CI21" t="inlineStr">
+        <is>
+          <t>1. length_words_raw | NEUTRAL | Tidak ada dampak signifikan (0.0518)
+2. char_repeat | NEUTRAL | Tidak ada dampak signifikan (0.0518)
+3. length_url | NEUTRAL | Tidak ada dampak signifikan (0.0239)
+4. length_hostname | NEUTRAL | Tidak ada dampak signifikan (0.0239)</t>
+        </is>
+      </c>
+      <c r="CJ21" t="inlineStr">
+        <is>
+          <t>URL `https://www.google.com` diklasifikasikan sebagai benign karena beberapa alasan:
+1. **Domain yang dikenal**: Google.com adalah domain yang sangat dikenal dan aman. Banyak orang menggunakan Google sebagai mesin pencari utama, dan domain ini telah terjamin keamanannya oleh organisasi keamanan internet seperti VeriSign.
+2. **Koneksi HTTPS**: URL menggunakan protokol HTTPS (Hypertext Transfer Protocol Secure), yang berarti bahwa komunikasi antara klien dan server dilindungi oleh sertifikat SSL/TLS (Secure Sockets Layer/Transport Layer Security). Ini menandakan bahwa data yang dikirimkan antara klien dan server telah dienkripsi dan aman.
+3. **Lack of URL parameter yang mencurigakan**: URL tidak memiliki parameter yang mencurigakan, seperti `utm_source` atau `utm_campaign`, yang sering digunakan oleh penipuan untuk melacak pengguna.
+4. **Domain tidak ambigu**: Domain `google.com` tidak ambigu dan tidak menyerupai domain penipuan yang umum.
+5. **Afiliasi yang jelas**: URL tidak memiliki afiliasi yang tidak jelas atau mengklaim bahwa situs tersebut memiliki afiliasi dengan Google.
+Dengan demikian, URL `https://www.google.com` dapat diklasifikasikan sebagai benign karena tidak memiliki indikasi penipuan atau keamanan yang tidak jelas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>https://www.apple.com</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>21</v>
+      </c>
+      <c r="F22" t="n">
+        <v>13</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>139</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>0.7841726618705036</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>0.2158273381294964</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>43.15789473684211</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>56.84210526315789</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY22" t="n">
+        <v>1</v>
+      </c>
+      <c r="BZ22" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH22" t="inlineStr">
+        <is>
+          <t>🟢 URL terdeteksi sebagai BENIGN dengan phishing probability 13.37% (BENIGN Range: 0.00-0.60). Benign Confidence: 86.63%. Top features: length_words_raw (0.043), char_repeat (0.043), length_url (0.023), length_hostname (0.023), google_index (0.013). Website ini AMAN untuk dikunjungi.</t>
+        </is>
+      </c>
+      <c r="CI22" t="inlineStr">
+        <is>
+          <t>1. length_words_raw | NEUTRAL | Tidak ada dampak signifikan (0.0434)
+2. char_repeat | NEUTRAL | Tidak ada dampak signifikan (0.0434)
+3. length_url | NEUTRAL | Tidak ada dampak signifikan (0.0233)
+4. length_hostname | NEUTRAL | Tidak ada dampak signifikan (0.0233)</t>
+        </is>
+      </c>
+      <c r="CJ22" t="inlineStr">
+        <is>
+          <t>Berikut beberapa alasan mengapa URL tersebut diklasifikasikan sebagai bening (benign):
+1. **Domain adalah domain publik**: Domain `.com` adalah domain publik yang umum digunakan untuk domain web komersial.
+2. **Perusahaan ternama**: Apple adalah perusahaan ternama yang sudah lama ada dan terkenal di seluruh dunia.
+3. **Tidak memiliki gejala malware**: URL tersebut tidak memiliki gejala malware, seperti link yang tidak biasa atau tidak terkait dengan domain.
+4. **Tidak memiliki gejala phishing**: URL tersebut tidak memiliki gejala phishing, seperti nama domain palsu yang mirip dengan domain asli Apple.
+5. **Tidak memiliki gejala ransomware**: URL tersebut tidak memiliki gejala ransomware, seperti perubahan ekstensi file yang tidak biasa.
+6. **URL yang valid**: URL tersebut memiliki struktur yang valid dan lengkap, dengan menggunakan protocol HTTPS (HyperText Transfer Protocol Secure), yang merupakan standar keamanan internet.
+Dengan melihat alasan di atas, URL tersebut diklasifikasikan sebagai bening karena tidak menunjukkan gejala kejahatan siber seperti malware, phishing, atau ransomware.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>https://www.wikipedia.org</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>25</v>
+      </c>
+      <c r="F23" t="n">
+        <v>17</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>376</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>0.005319148936170213</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>0.9946808510638298</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>42.85714285714285</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU23" t="n">
+        <v>0.5319148936170213</v>
+      </c>
+      <c r="BV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY23" t="n">
+        <v>1</v>
+      </c>
+      <c r="BZ23" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH23" t="inlineStr">
+        <is>
+          <t>🟢 URL terdeteksi sebagai BENIGN dengan phishing probability 5.05% (BENIGN Range: 0.00-0.60). Benign Confidence: 94.95%. Top features: char_repeat (0.056), length_words_raw (0.056), length_url (0.024), length_hostname (0.024), google_index (0.019). Website ini AMAN untuk dikunjungi.</t>
+        </is>
+      </c>
+      <c r="CI23" t="inlineStr">
+        <is>
+          <t>1. char_repeat | NEUTRAL | Tidak ada dampak signifikan (0.0562)
+2. length_words_raw | NEUTRAL | Tidak ada dampak signifikan (0.0562)
+3. length_url | NEUTRAL | Tidak ada dampak signifikan (0.0244)
+4. length_hostname | NEUTRAL | Tidak ada dampak signifikan (0.0244)</t>
+        </is>
+      </c>
+      <c r="CJ23" t="inlineStr">
+        <is>
+          <t>URL https://www.wikipedia.org diklasifikasikan sebagai benign karena beberapa alasan:
+1. **Domain nama yang jelas**: URL tersebut memiliki domain nama yang jelas dan dapat dibaca dengan mudah, yaitu wikipedia.org. Domain nama ini tidak memiliki ekstensi yang mencurigakan dan tidak tampaknya sebagai link spam atau malware.
+2. **Kemungkinan sumber yang terpercaya**: Wikipedia adalah sebuah sumber informasi yang terpercaya dan dapat dipercaya. Situs webnya juga memiliki reputation yang baik dan telah terbukti menjadi salah satu sumber informasi terpercaya di dunia.
+3. **Lencana keamanan yang valid**: Situs web Wikipedia memiliki lencana keamanan SSL/TLS yang valid, yaitu HTTPS. Lencana keamanan ini menandakan bahwa data yang dikirimkan ke situs web tersebut akan dikripsi dan aman dari intervensi pihak ketiga.
+4. **Struktur URL yang normal**: Struktur URL tersebut juga memiliki pola yang normal, yaitu memiliki subsitus berikut `www`, diikuti oleh nama domain yang relevan.
+5. **Konten yang relevan**: Konten di halaman utama Wikipedia juga relevan dengan domain nama itu sendiri, yaitu informasi tentang ensiklopedia.
+Dengan demikian, URL tersebut diklasifikasikan sebagai benign karena memiliki karakteristik yang menunjukkan bahwa situs web tersebut aman, terpercaya, dan relevan dengan isi konten yang ditujukan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>www.dghjdgf.com/paypal.co.uk/cycgi-bin/webscrcmd=_home-customer&amp;nav=1/loading.php</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>phishing</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>88</v>
+      </c>
+      <c r="F24" t="n">
+        <v>15</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>5</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" t="n">
+        <v>2</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>6</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0.01136363636363636</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>4.375</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>4.333333333333333</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>4.416666666666667</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH24" t="inlineStr">
+        <is>
+          <t>🔴 URL terdeteksi sebagai PHISHING dengan phishing probability 79.35% (PHISHING Range: 0.60-1.00). Top features: nb_and (0.448), nb_qm (0.448), ratio_digits_host (0.073), ratio_digits_url (0.073), nb_space (0.033). Website ini TIDAK AMAN untuk dikunjungi.</t>
+        </is>
+      </c>
+      <c r="CI24" t="inlineStr">
+        <is>
+          <t>1. nb_and | NEUTRAL | Tidak ada dampak signifikan (0.4484)
+2. nb_qm | NEUTRAL | Tidak ada dampak signifikan (0.4484)
+3. ratio_digits_host | NEUTRAL | Tidak ada dampak signifikan (0.0733)
+4. ratio_digits_url | NEUTRAL | Tidak ada dampak signifikan (0.0733)
+5. nb_space | NEUTRAL | Tidak ada dampak signifikan (0.0331)</t>
+        </is>
+      </c>
+      <c r="CJ24" t="inlineStr">
+        <is>
+          <t>URL yang Anda berikan dapat diklasifikasikan sebagai phishing karena beberapa alasan:
+1. **Domain yang tidak biasa**: URL tersebut menggunakan domain yang tidak biasa dan tidak familiar ("dghjdgf.com") untuk mengklonkan situs PayPal (pay pal.co.uk). Domain asli PayPal adalah "paypal.com" atau "www.paypal.com".
+2. **Penggunaan tanda baca yang tidak tepat**: URL tersebut menggunakan tanda baca yang tidak tepat, seperti "dghjdgf.com/paypal.co.uk" dan "_home-customer" yang memiliki titik di awal. Format URL yang benar biasanya menggunakan tanda baca yang tepat dan tidak memiliki titik di awal.
+3. **Penggunaan istilah "cycgi-bin" yang tidak biasa**: Istilah "cycgi-bin" seharusnya adalah "cgi-bin", yang adalah kode untuk folder "Common Gateway Interface Binaries" pada server web.
+4. **Penggunaan "webscrcmd" yang tidak biasa**: Istilah "webscrcmd" tidak biasa digunakan dalam URL, dan "webscrcmd=_home-customer" tampak seperti kode yang tidak jelas.
+5. **Penggunaan "_home-customer" yang seperti kode**: Penggunaan "_" (garis bawah) sebelum kata "customer" seperti kode, bukan seperti kata biasa.
+6. **Penggunaan "_loading.php" yang seperti kode**: Penggunaan "_" (garis bawah) sebelum kata "loading" seperti kode, bukan seperti kata biasa.
+Dengan demikian, URL tersebut dapat diklasifikasikan sebagai phishing karena mengklonkan situs PayPal dengan cara yang tidak biasa dan menggunaan kode yang tidak jelas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>https://smmhejtkx.olghvlbkcdqtscd.top/ksjdbj</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>phishing</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>44</v>
+      </c>
+      <c r="F25" t="n">
+        <v>29</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH25" t="inlineStr">
+        <is>
+          <t>🔴 URL terdeteksi sebagai PHISHING dengan phishing probability 20.00% (PHISHING Range: 0.60-1.00). 2 fitur utama menunjukkan indikator phishing berbahaya. Website ini TIDAK AMAN untuk dikunjungi.</t>
+        </is>
+      </c>
+      <c r="CI25" t="inlineStr">
+        <is>
+          <t>1. ip | BENIGN | ip = 0 (tidak ada indikator phishing) ()
+2. nb_at | BENIGN | nb_at = 0 (tidak ada indikator phishing) ()
+3. suspicious_tld | PHISHING | TLD mencurigakan ()
+4. random_domain | PHISHING | Domain terlihat random/tidak punya pola ()
+5. shortening_service | BENIGN | shortening_service = 0 (tidak ada indikator phishing) ()</t>
+        </is>
+      </c>
+      <c r="CJ25" t="inlineStr">
+        <is>
+          <t>URL tersebut diklasifikasikan sebagai phishing karena beberapa alasan:
+1. **Domain tidak jelas**: URL tersebut memiliki domain yang tidak biasa, yaitu `smmhejtkx.olghvlbkcdqtscd.top`. Domain seperti ini biasanya tidak memiliki identitas yang jelas dan tidak diketahui oleh layanan DNS yang berlaku umum.
+2. **TLD tidak biasa**: URL tersebut menggunakan TLD (Top-Level Domain) `top`, yang tidak biasa digunakan untuk domain yang kredibel. Biasanya, domain yang kredibel menggunakan TLD seperti `.com`, `.org`, `.net`, dll.
+3. **Karakter tidak biasa**: URL tersebut memiliki karakter yang tidak biasa, seperti `smmhejtkx` dan `olghvlbkcdqtscd`. Karakter-karakter seperti ini biasanya digunakan untuk membuat URL yang sulit dibaca dan sulit dikenali sebagai phishing.
+4. **Kata kunci tidak jelas**: URL tersebut tidak jelas apa yang ditawarkan atau disediakan. Biasanya, URL phishing memiliki kata kunci seperti "login", "signup", "reset password", dll.
+5. **Predikat tidak jelas**: URL tersebut tidak memiliki predikat yang jelas, seperti "example" atau "myaccount". Predikat seperti ini biasanya digunakan untuk membuat URL yang lebih jelas dan lebih kredibel.
+Dengan demikian, URL tersebut sebaiknya dihindari karena kemungkinan besar akan membawa Anda ke situs web phishing yang berusaha untuk mencuri informasi pribadi Anda atau melakukan penipuan lainnya.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>https://secure-login.verify.paypal.account-update.phishingsite.com</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>phishing</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>66</v>
+      </c>
+      <c r="F26" t="n">
+        <v>58</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>5</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>6.222222222222222</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>6.375</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH26" t="inlineStr">
+        <is>
+          <t>🔴 URL terdeteksi sebagai PHISHING dengan phishing probability 95.68% (PHISHING Range: 0.60-1.00). Top features: nb_qm (0.210), nb_and (0.210), nb_dots (0.144), ip (0.144), length_hostname (0.027). 1 fitur utama menunjukkan indikator phishing berbahaya. Website ini TIDAK AMAN untuk dikunjungi.</t>
+        </is>
+      </c>
+      <c r="CI26" t="inlineStr">
+        <is>
+          <t>1. nb_qm | NEUTRAL | Tidak ada dampak signifikan (0.2096)
+2. nb_and | NEUTRAL | Tidak ada dampak signifikan (0.2096)
+3. nb_dots | NEUTRAL | Tidak ada dampak signifikan (0.1441)
+4. ip | BENIGN | ip = 0 (tidak ada indikator phishing) (0.1441)
+5. length_hostname | PHISHING | Hostname terlalu panjang (0.0266)</t>
+        </is>
+      </c>
+      <c r="CJ26" t="inlineStr">
+        <is>
+          <t>URL tersebut diklasifikasikan sebagai phishing karena beberapa alasan:
+1. **Nama domain yang tidak biasa**: PayPal biasanya memiliki domain di paypal.com, bukan verify.paypal.account-update.phishingsite.com. Nama domain ini terlihat tidak biasa dan tidak jelas.
+2. **Kata "phishingsite"**: Kata "phishingsite" langsung mencolok dan menunjukkan bahwa situs ini tidak dapat dipercaya.
+3. **Kata "update"**: Kata "update" dapat membuat Anda berpikir bahwa situs ini ingin mengupdate informasi Anda, tetapi sebenarnya itu adalah cara untuk mengeksploitasi kepercayaan Anda.
+4. **Kata "secure-login"**: Kata "secure-login" dapat membuat Anda berpikir bahwa situs ini aman, tetapi sebenarnya itu adalah cara untuk menipu Anda untuk memasukkan informasi login Anda.
+5. **URL yang panjang dan kompleks**: URL yang panjang dan kompleks seringkali merupakan ciri-ciri url phishing.
+Dalam keseluruhan, URL tersebut memiliki beberapa ciri-ciri yang dapat menunjukkan bahwa situs tersebut adalah phishing site. Oleh karena itu, Anda sebaiknya tidak mengakses situs tersebut dan melaporkannya ke tim keamanan PayPal atau situs lainnya untuk mencegah kasus penipuan lebih lanjut.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>http://192.168.1.1/amazon-login@phishing-secure.com</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>phishing</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>51</v>
+      </c>
+      <c r="F27" t="n">
+        <v>11</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" t="n">
+        <v>4</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0.1568627450980392</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH27" t="inlineStr">
+        <is>
+          <t>🔴 URL terdeteksi sebagai PHISHING dengan phishing probability 0.00% (PHISHING Range: 0.60-1.00). 2 fitur utama menunjukkan indikator phishing berbahaya. Website ini TIDAK AMAN untuk dikunjungi.</t>
+        </is>
+      </c>
+      <c r="CI27" t="inlineStr">
+        <is>
+          <t>1. ip | PHISHING | IP address digunakan di URL ()
+2. nb_at | PHISHING | @ symbol dalam URL ()
+3. suspicious_tld | BENIGN | suspicious_tld = 0 (tidak ada indikator phishing) ()
+4. random_domain | BENIGN | random_domain = 0 (tidak ada indikator phishing) ()
+5. shortening_service | BENIGN | shortening_service = 0 (tidak ada indikator phishing) ()</t>
+        </is>
+      </c>
+      <c r="CJ27" t="inlineStr">
+        <is>
+          <t>URL tersebut diklasifikasikan sebagai phishing karena beberapa alasan:
+1. **Penamaan Domain yang Salah**: URL tersebut memiliki penamaan domain yang salah ("phishing-secure.com") yang dapat menipu pengguna untukpercaya bahwa itu adalah situs web yang aman dan dapat dipercaya. Namun, dalam kenyataannya, URL tersebut dapat berbeda dengan situs web aslinya yang biasanya digunakan untuk login ("amazon.com").
+2. **Kombinasi Simbol dan Karakter**: URL tersebut menggunakan kombinasi simbol (@) dan karater (.com) yang bisa menunjukkan bahwa URL tersebut tidak resmi.
+3. **Alamat IP statis**: URL tersebut menggunakan alamat IP statis (192.168.1.1) yang biasanya digunakan oleh router dan modem untuk mengakses pengaturan jaringan, bukan untuk mengakses situs web yang berisi form login.
+4. **Penambahan Simbol dan Karater pada URL**: Penambahan simbol "@" dan ".com" pada URL tersebut menunjukkan bahwa URL tersebut tidak asli.
+Dengan demikian, URL tersebut dapat dianggap sebagai phishing karena menunjukkan ciri-ciri yang tidak biasa dan dapat menipu pengguna untuk memberikan informasi pribadi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>http://192.168.1.1/amazon-login@phishing-secure.com</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>phishing</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>51</v>
+      </c>
+      <c r="F28" t="n">
+        <v>11</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" t="n">
+        <v>4</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>3</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0.1568627450980392</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH28" t="inlineStr">
+        <is>
+          <t>🔴 URL terdeteksi sebagai PHISHING dengan phishing probability 0.00% (PHISHING Range: 0.60-1.00). 2 fitur utama menunjukkan indikator phishing berbahaya. Website ini TIDAK AMAN untuk dikunjungi.</t>
+        </is>
+      </c>
+      <c r="CI28" t="inlineStr">
+        <is>
+          <t>1. ip | PHISHING | IP address digunakan di URL ()
+2. nb_at | PHISHING | @ symbol dalam URL ()
+3. suspicious_tld | BENIGN | suspicious_tld = 0 (tidak ada indikator phishing) ()
+4. random_domain | BENIGN | random_domain = 0 (tidak ada indikator phishing) ()
+5. shortening_service | BENIGN | shortening_service = 0 (tidak ada indikator phishing) ()</t>
+        </is>
+      </c>
+      <c r="CJ28" t="inlineStr">
+        <is>
+          <t>URL yang disebutkan dapat diklasifikasikan sebagai phishing karena beberapa alasan:
+1. **Penyamaran**: URL tersebut tampak seperti URL asli Amazon (amazon.com), tetapi memiliki beberapa kesalahan sintaks dan struktur yang tidak biasa. Hal ini dapat membuat pengguna percaya bahwa mereka sedang mengakses situs asli Amazon.
+2. **Penggunaan simbol "@" yang tidak biasa**: Simbol "@" biasanya digunakan untuk menghubungkan domain dengan subdomain, tetapi dalam kasus ini, "@" digunakan sebagai bagian dari URL. Hal ini membuat URL terlihat tidak biasa dan dapat menimbulkan kecurigaan.
+3. **Penggunaan "192.168.1.1" sebagai domain**: "192.168.1.1" adalah alamat IP umum untuk router perumahan dan bukan domain yang biasa digunakan dalam URL. Hal ini dapat membuat pengguna merasa bahwa mereka sedang mengakses alamat IP router mereka sendiri.
+4. **Kombinasi dengan kata "phishing-secure.com"**: Kombinasi kata "phishing-secure" dengan domain ".com" yang biasa digunakan membuat URL terlihat seperti situs web yang aman dan terpercaya. Namun, hal ini sebenarnya adalah strategi phishing untuk membuat pengguna merasa aman dan terjebak.
+5. **Kurangnya https**: URL tersebut tidak menggunakan "https" yang biasa digunakan untuk situs web yang aman dan terpercaya. Hal ini dapat membuat pengguna merasa bahwa situs web tersebut tidak aman.
+Dalam keseluruhan, URL yang disebutkan dapat diklasifikasikan sebagai phishing karena memiliki beberapa karakteristik yang tidak biasa dan dapat menimbulkan kecurigaan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>https://www.google.com</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>22</v>
+      </c>
+      <c r="F29" t="n">
+        <v>14</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>12</v>
+      </c>
+      <c r="BI29" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="BJ29" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="BK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ29" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY29" t="n">
+        <v>1</v>
+      </c>
+      <c r="BZ29" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH29" t="inlineStr">
+        <is>
+          <t>🟢 URL terdeteksi sebagai BENIGN dengan phishing probability 33.38% (BENIGN Range: 0.00-0.60). Benign Confidence: 66.62%. Top features: length_words_raw (0.052), char_repeat (0.052), length_url (0.024), length_hostname (0.024), web_traffic (0.019). 1 fitur utama menunjukkan karakteristik website legitimate. Website ini AMAN untuk dikunjungi.</t>
+        </is>
+      </c>
+      <c r="CI29" t="inlineStr">
+        <is>
+          <t>1. length_words_raw | NEUTRAL | Tidak ada dampak signifikan (0.0518)
+2. char_repeat | NEUTRAL | Tidak ada dampak signifikan (0.0518)
+3. length_url | BENIGN | URL length normal (0.0239)
+4. length_hostname | NEUTRAL | Tidak ada dampak signifikan (0.0239)</t>
+        </is>
+      </c>
+      <c r="CJ29" t="inlineStr">
+        <is>
+          <t>URL tersebut diklasifikasikan sebagai "benign" atau tidak berbahaya karena beberapa alasan:
+1. **Domain yang terverifikasi**: URL tersebut menggunakan domain yang terverifikasi dan terdaftar secara resmi (google.com). Domain yang terverifikasi seringkali memiliki reputasi baik dan aman untuk diakses.
+2. **Tidak mengandung kata-kata yang biasa digunakan untuk phishing**: URL tersebut tidak mengandung kata-kata yang biasa digunakan untuk phishing, seperti "bonus", "gratis", atau "saya". Kata-kata tersebut seringkali digunakan oleh penjahat siber untuk menipu pengguna dan meminta informasi sensitif.
+3. **Tidak mengandung tautan langsung ke konten eksplisit**: URL tersebut tidak mengandung tautan langsung ke konten eksplisit atau kasar. Jika URL tersebut mengandung tautan langsung ke konten eksplisit, kemungkinan besar akan diklasifikasikan sebagai "banned" atau berbahaya.
+4. **Menggunakan HTTPS**: URL tersebut menggunakan protokol HTTPS (Hypertext Transfer Protocol Secure), yang menjamin komunikasi antara pengguna dan server dalam jaringan yang aman dan enkripsi. Kebanyakan browser modern telah melakukan pemindaian keamanan yang dapat mendeteksi perbedaan antara jaringan HTTP dan HTTPS.
+5. **Dapat dibuka secara langsung**: URL tersebut dapat dibuka secara langsung tanpa perlu memasukkan username atau password, dan tidak ada peringatan keamanan yang menunjukkan bahwa URL tersebut berbahaya.
+Dengan demikian, URL tersebut dapat diklasifikasikan sebagai "benign" atau tidak berbahaya karena sudah terverifikasi dan memiliki reputasi baik.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>https://www.microsoft.com</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>25</v>
+      </c>
+      <c r="F30" t="n">
+        <v>17</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>101</v>
+      </c>
+      <c r="BI30" t="n">
+        <v>0.5643564356435643</v>
+      </c>
+      <c r="BJ30" t="n">
+        <v>0.4356435643564356</v>
+      </c>
+      <c r="BK30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP30" t="n">
+        <v>43.61702127659575</v>
+      </c>
+      <c r="BQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR30" t="n">
+        <v>100</v>
+      </c>
+      <c r="BS30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU30" t="n">
+        <v>1.98019801980198</v>
+      </c>
+      <c r="BV30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BZ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH30" t="inlineStr">
+        <is>
+          <t>🟢 URL terdeteksi sebagai BENIGN dengan phishing probability 9.91% (BENIGN Range: 0.00-0.60). Benign Confidence: 90.09%. Top features: length_words_raw (0.047), char_repeat (0.047), length_hostname (0.026), length_url (0.026), google_index (0.019). 1 fitur utama menunjukkan karakteristik website legitimate. Website ini AMAN untuk dikunjungi.</t>
+        </is>
+      </c>
+      <c r="CI30" t="inlineStr">
+        <is>
+          <t>1. length_words_raw | NEUTRAL | Tidak ada dampak signifikan (0.0466)
+2. char_repeat | NEUTRAL | Tidak ada dampak signifikan (0.0466)
+3. length_hostname | NEUTRAL | Tidak ada dampak signifikan (0.0256)
+4. length_url | BENIGN | URL length normal (0.0256)</t>
+        </is>
+      </c>
+      <c r="CJ30" t="inlineStr">
+        <is>
+          <t>URL "https://www.microsoft.com" diklasifikasikan sebagai benign karena beberapa alasan:
+1. **Domain Penerimaan**: URL tersebut menunjukkan bahwa domain adalah "microsoft.com", yang merupakan domain yang sah dan diakui secara internasional. Domain ini dimiliki dan dioperasikan oleh Microsoft, sebuah perusahaan besar yang terpercaya.
+2. **Karakteristik Bahasa**: URL tersebut memiliki karakteristik bahasa yang umum dan tidak mencurigakan, seperti penggunaan huruf-kata yang sah dan tidak ada istilah-istilah yang mencurigakan atau tidak biasa.
+3. **Ketersediaan di Internet**: Domain "microsoft.com" sangat populer dan mudah diakses melalui internet. URL tersebut dapat dibuka langsung pada browser web tanpa ada masalah atau gangguan.
+4. **Lack of URL Suspicious**: URL tidak memiliki fitur-fitur yang biasanya digunakan oleh penjahat siber, seperti penggunaan huruf-huruf yang tidak biasa, menggunakan karakter-karakter spesial, atau penggunaan URL yang sangat panjang dan kompleks.
+5. **Konten yang Tervalidasi**: Konten yang disajikan oleh URL tersebut umumnya merupakan konten yang valid dan akurat, seperti informasi produk, dokumentasi, dan lain-lain.
+Dengan demikian, URL "https://www.microsoft.com" diklasifikasikan sebagai benign karena tidak memiliki kemungkinan yang tinggi untuk mengandung kerentanan atau serangan siber.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>http://192.168.1.1/amazon-login@phishing-secure.com</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>phishing</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>51</v>
+      </c>
+      <c r="F31" t="n">
+        <v>11</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" t="n">
+        <v>4</v>
+      </c>
+      <c r="I31" t="n">
+        <v>2</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0.1568627450980392</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH31" t="inlineStr">
+        <is>
+          <t>🔴 URL terdeteksi sebagai PHISHING dengan phishing probability 0.00% (PHISHING Range: 0.60-1.00). 2 fitur utama menunjukkan indikator phishing berbahaya. Website ini TIDAK AMAN untuk dikunjungi.</t>
+        </is>
+      </c>
+      <c r="CI31" t="inlineStr">
+        <is>
+          <t>1. ip | PHISHING | IP address digunakan di URL ()
+2. nb_at | PHISHING | @ symbol dalam URL ()
+3. suspicious_tld | BENIGN | suspicious_tld = 0 (tidak ada indikator phishing) ()
+4. random_domain | BENIGN | random_domain = 0 (tidak ada indikator phishing) ()
+5. shortening_service | BENIGN | shortening_service = 0 (tidak ada indikator phishing) ()</t>
+        </is>
+      </c>
+      <c r="CJ31" t="inlineStr">
+        <is>
+          <t>URL tersebut diklasifikasikan sebagai phishing karena memiliki beberapa karakteristik yang mencurigakan:
+1. **Alamat IP**: Alamat IP adalah `192.168.1.1`, yang biasanya digunakan sebagai alamat IP router atau modem router di rumah atau kantor. Alamat ini tidak biasanya dihubungkan dengan situs web atau aplikasi online yang kredibel, seperti Amazon.
+2. **Nama subdomain**: Nama subdomain adalah `amazon-login@phishing-secure.com`. Ada dua hal yang mencurigakan di sini:
+ * **@simbol**: Simbol `@` biasanya digunakan sebagai separator antara nama pengguna dan nama domain, seperti `nama pengguna@domain.com`. Namun, dalam kasus ini, simbol `@` digunakan sebagai bagian dari nama subdomain, yang tidak biasanya dilakukan.
+ * **Nama subdomain tidak mencerminkan identitas**: Nama subdomain `amazzon-login` dapat membuat Anda berpikir bahwa halaman tersebut adalah login resmi Amazon. Namun, kombinasi nama subdomain dengan domain `phishing-secure.com` mencurigakan karena domain tersebut tidak memiliki koneksi yang jelas dengan Amazon.
+3. **Kombinasi dengan domain phishing**: Domain `phishing-secure.com` secara eksplisit mengacu pada kegiatan phishing. Domain ini tidak kredibel dan tidak dapat dipercaya untuk situs web yang aman.
+Dengan kombinasi dari beberapa faktor di atas, URL tersebut dapat diklasifikasikan sebagai phishing karena memiliki tujuan untuk menipu pengguna mencapai halaman palsu yang berhubungan dengan Amazon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>https://cis.del.ac.id/</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>phishing</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>22</v>
+      </c>
+      <c r="F32" t="n">
+        <v>13</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>3</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>3</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN32" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ32" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH32" t="inlineStr">
+        <is>
+          <t>🔴 URL terdeteksi sebagai PHISHING dengan phishing probability 93.85% (PHISHING Range: 0.60-1.00). Top features: char_repeat (0.047), length_words_raw (0.047), dns_record (0.020), google_index (0.020), length_hostname (0.019). Website ini TIDAK AMAN untuk dikunjungi.</t>
+        </is>
+      </c>
+      <c r="CI32" t="inlineStr">
+        <is>
+          <t>1. char_repeat | NEUTRAL | Tidak ada dampak signifikan (0.0472)
+2. length_words_raw | NEUTRAL | Tidak ada dampak signifikan (0.0472)
+3. length_hostname | NEUTRAL | Tidak ada dampak signifikan (0.019)</t>
+        </is>
+      </c>
+      <c r="CJ32" t="inlineStr">
+        <is>
+          <t>Alamat URL yang Anda berikan yaitu `https://cis.del.ac.id/` tidak sepenuhnya dapat diklasifikasikan sebagai phishing, karena tidak ada informasi yang jelas bahwa URL tersebut berisiko.
+Namun, saya dapat memberikan beberapa kemungkinan penjelasan mengapa URL tersebut mungkin diklasifikasikan sebagai phishing:
+1. **Keasalan**: Tidak ada informasi tentang domain `cis.del.ac.id` yang jelas, sehingga tidak dapat dipastikan keasalan atau tujuan dari URL tersebut.
+2. **Distribusi spam**: Domain `del.ac.id` mungkin terdapat domain yang digunakan untuk kegiatan spam atau phishing.
+3. **Kloning domain**: URL tersebut mungkin merupakan kloning dari website yang asli, dengan tujuan untuk mencuri informasi pribadi atau menginstal malware.
+Untuk memastikan apakah URL tersebut aman atau tidak, Anda dapat melakukan beberapa tindakan berikut:
+1. **Periksa reputasi domain**: Gunakan layanan periksa reputasi domain seperti VirusTotal atau SimilarWeb untuk melihat riwayat aktivitas domain tersebut.
+2. **Periksa sertifikat SSL**: Pastikan bahwa sertifikat SSL yang digunakan oleh website tersebut adalah yang valid dan dikeluarkan oleh CA (Certificate Authority) yang terpercaya.
+3. **Periksa URL**: Periksa apakah URL tersebut merupakan URL yang resmi dan tidak ada perubahan yang tidak biasa.
+4. **Jangan menyimpan username dan password**: Jangan menyimpan username dan password di browser atau di aplikasi yang terhubung dengan URL tersebut.
+Jika Anda masih ragu-ragu, sebaiknya untuk berhati-hati dan tidak mengakses URL tersebut.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>https://github.com/</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>19</v>
+      </c>
+      <c r="F33" t="n">
+        <v>10</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>3</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH33" t="n">
+        <v>152</v>
+      </c>
+      <c r="BI33" t="n">
+        <v>0.9144736842105263</v>
+      </c>
+      <c r="BJ33" t="n">
+        <v>0.08552631578947369</v>
+      </c>
+      <c r="BK33" t="n">
+        <v>19</v>
+      </c>
+      <c r="BL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO33" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP33" t="n">
+        <v>89.47368421052632</v>
+      </c>
+      <c r="BQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR33" t="n">
+        <v>100</v>
+      </c>
+      <c r="BS33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU33" t="n">
+        <v>6.578947368421052</v>
+      </c>
+      <c r="BV33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY33" t="n">
+        <v>1</v>
+      </c>
+      <c r="BZ33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH33" t="inlineStr">
+        <is>
+          <t>🟢 URL terdeteksi sebagai BENIGN dengan phishing probability 26.40% (BENIGN Range: 0.00-0.60). Benign Confidence: 73.60%. Top features: char_repeat (0.053), length_words_raw (0.053), dns_record (0.024), google_index (0.024), length_hostname (0.020). Website ini AMAN untuk dikunjungi.</t>
+        </is>
+      </c>
+      <c r="CI33" t="inlineStr">
+        <is>
+          <t>1. char_repeat | NEUTRAL | Tidak ada dampak signifikan (0.0529)
+2. length_words_raw | NEUTRAL | Tidak ada dampak signifikan (0.0529)
+3. length_hostname | NEUTRAL | Tidak ada dampak signifikan (0.0205)</t>
+        </is>
+      </c>
+      <c r="CJ33" t="inlineStr">
+        <is>
+          <t>URL tersebut diklasifikasikan sebagai bening karena beberapa alasan:
+1. **Tidak mengandung kata-kata mencurigakan**: URL tersebut tidak mengandung kata-kata seperti "malware", "virus", "ransomware", atau "exploit" yang biasanya terkait dengan konten berbahaya.
+2. **Mengarah ke GitHub**: GitHub adalah sebuah platform penyebaran kode sumber terkemuka dan digunakan oleh banyak pengembang sebagai tempat menyimpan dan berbagi kode sumber proyek mereka. URL tersebut mengarah ke alamat GitHub yang sah.
+3. **Tidak memiliki tanda tanya atau simbol lain yang mencurigakan**: URL tersebut tidak memiliki tanda tanya, garis bawah, atau simbol lain yang dapat menandakan bahwa URL tersebut adalah sebuah trik atau aksi kejam.
+4. **Memiliki ekstensi ".com" yang sah**: URL tersebut memiliki ekstensi ".com" yang merupakan ekstensi domain top-level yang sah dan umum digunakan.
+5. **Menggunakan format URL yang benar**: URL tersebut menggunakan format URL yang benar, dengan domain, port, jalur, parameter, dan kode status (200 OK) yang sah.
+Dengan demikian, URL tersebut dapat diklasifikasikan sebagai bening karena tidak mengandung konten yang mencurigakan, mengarah ke platform yang sah, dan memiliki format URL yang benar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>http://paypal-verify-account-urgent.suspicious.tk</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>phishing</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>49</v>
+      </c>
+      <c r="F34" t="n">
+        <v>42</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I34" t="n">
+        <v>3</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>5.857142857142857</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>6.166666666666667</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH34" t="inlineStr">
+        <is>
+          <t>🔴 URL terdeteksi sebagai PHISHING dengan phishing probability 10.00% (PHISHING Range: 0.60-1.00). 1 fitur utama menunjukkan indikator phishing berbahaya. Website ini TIDAK AMAN untuk dikunjungi.</t>
+        </is>
+      </c>
+      <c r="CI34" t="inlineStr">
+        <is>
+          <t>1. ip | BENIGN | ip = 0 (tidak ada indikator phishing) ()
+2. nb_at | BENIGN | nb_at = 0 (tidak ada indikator phishing) ()
+3. suspicious_tld | PHISHING | TLD mencurigakan ()
+4. random_domain | BENIGN | random_domain = 0 (tidak ada indikator phishing) ()
+5. shortening_service | BENIGN | shortening_service = 0 (tidak ada indikator phishing) ()</t>
+        </is>
+      </c>
+      <c r="CJ34" t="inlineStr">
+        <is>
+          <t>URL yang Anda berikan (http://paypal-verify-account-urgent.suspicious.tk) dapat diklasifikasikan sebagai phishing karena beberapa alasan berikut:
+1. **Penamaan tidak resmi**: URL tersebut memiliki penamaan yang tidak resmi dan tidak resmi, yaitu "paypal-verify-account-urgent". PayPal adalah perusahaan pembayaran online yang populer, namun URL tersebut tidak berasal dari perusahaan tersebut. Penamaan semacam ini dapat digunakan untuk menipu pengguna bahwa mereka sedang berinteraksi dengan PayPal.
+2. **Dengan sufiks yang tidak akrab**: Sufiks ".suspicious.tk" adalah sufiks tambahan yang menunjukkan bahwa situs tersebut memiliki reputasi buruk atau tidak diandalkan. Sufiks ini dapat digunakan untuk menimbulkan kesan bahwa situs tersebut berisiko atau tidak dapat diandalkan.
+3. **Tidak ada keamanan SSL**: URL tersebut tidak memiliki indikasi adanya SSL (Secure Sockets Layer) atau TLS (Transport Layer Security), yang berarti bahwa data yang dikirim melalui URL tersebut tidak aman dan dapat dibaca oleh pihak ketiga.
+4. **Mengharapkan aksi segera**: Kata "urgent" dalam URL tersebut menimbulkan tekanan pada pengguna untuk mengambil tindakan segera, seperti memverifikasi akun mereka. Ini adalah teknik phishing yang umum digunakan untuk menipu pengguna.
+5. **Penipuan kepada pelanggan PayPal**: URL tersebut menargetkan pelanggan PayPal, dengan menawarkan mereka untuk memverifikasi akun mereka. Namun, URL tersebut tidak berasal dari PayPal resmi, sehingga merupakan contoh dari phishing.
+Dengan demikian, URL tersebut dapat diklasifikasikan sebagai phishing karena memiliki beberapa ciri-ciri yang tidak aman dan dapat merugikan pengguna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="129.6" customHeight="1">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>www.dghjdgf.com/paypal.co.uk/cycgi-bin/webscrcmd=_home-customer&amp;nav=1/loading.php</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>phishing</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>88</v>
+      </c>
+      <c r="F35" t="n">
+        <v>15</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>5</v>
+      </c>
+      <c r="I35" t="n">
+        <v>2</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1</v>
+      </c>
+      <c r="M35" t="n">
+        <v>2</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>6</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0.01136363636363636</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>4.375</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>4.333333333333333</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>4.416666666666667</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH35" t="inlineStr">
+        <is>
+          <t>🔴 URL terdeteksi sebagai PHISHING dengan phishing probability 79.35% (PHISHING Range: 0.60-1.00). Top features: nb_and (0.448), nb_qm (0.448), ratio_digits_host (0.073), ratio_digits_url (0.073), nb_space (0.033). Website ini TIDAK AMAN untuk dikunjungi.</t>
+        </is>
+      </c>
+      <c r="CI35" t="inlineStr">
+        <is>
+          <t>1. nb_and | NEUTRAL | Tidak ada dampak signifikan (0.4484)
+2. nb_qm | NEUTRAL | Tidak ada dampak signifikan (0.4484)
+3. ratio_digits_host | NEUTRAL | Tidak ada dampak signifikan (0.0733)
+4. ratio_digits_url | NEUTRAL | Tidak ada dampak signifikan (0.0733)
+5. nb_space | NEUTRAL | Tidak ada dampak signifikan (0.0331)</t>
+        </is>
+      </c>
+      <c r="CJ35" s="1" t="inlineStr">
+        <is>
+          <t>URL yang Anda berikan dapat diklasifikasikan sebagai phishing karena beberapa alasan:
+1. **Domain yang tidak sah**: URL tersebut menggunakan domain `dghjdgf.com` yang tidak sah (tidak terkait dengan nama perusahaan PayPal) untuk melayani halaman "paypal.co.uk". Hal ini dapat menipu pengguna bahwa mereka berada di situs PayPal yang resmi.
+2. **Tautan yang tidak jelas**: URL tersebut memiliki tautan berikut: `cycgi-bin/webscrcmd=_home-customer&amp;nav=1/loading.php`. Tautan ini tidak jelas dan tidak dapat dikenali sebagai tautan yang biasa digunakan oleh PayPal.
+3. **Penulisan yang tidak konsisten**: URL tersebut menggunakan kombinasi dari huruf huruf besar dan kecil, serta memiliki penulisan yang tidak konsisten. Hal ini menunjukkan bahwa URL tersebut tidak merupakan URL yang resmi.
+4. **Kesamaan dengan URL PayPal yang sebenarnya**: URL PayPal yang sebenarnya biasanya memiliki struktur `https://www.paypal.co.uk` atau `https://www.paypal.com`. URL tersebut memiliki struktur yang mirip, tetapi dengan penambahan `cycgi-bin/webscrcmd=_home-customer&amp;nav=1/loading.php` yang tidak jelas.
+Dengan demikian, URL tersebut dapat diklasifikasikan sebagai phishing karena dapat menipu pengguna untuk merekam alamat email, kata sandi, ataupun informasi keuangan lainnya tanpa sepengetahuan mereka sendiri.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>http://192.168.1.1/amazon-login@phishing-secure.com</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>phishing</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>51</v>
+      </c>
+      <c r="F36" t="n">
+        <v>11</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" t="n">
+        <v>4</v>
+      </c>
+      <c r="I36" t="n">
+        <v>2</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>3</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0.1568627450980392</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH36" t="inlineStr">
+        <is>
+          <t>🔴 URL terdeteksi sebagai PHISHING dengan phishing probability 0.00% (PHISHING Range: 0.60-1.00). 3 fitur utama menunjukkan indikator phishing berbahaya. Website ini TIDAK AMAN untuk dikunjungi.</t>
+        </is>
+      </c>
+      <c r="CI36" t="inlineStr">
+        <is>
+          <t>1. ip | PHISHING | IP address digunakan di URL ()
+2. nb_at | PHISHING | @ symbol dalam URL ()
+3. phish_hints | PHISHING | Mengandung hint phishing (login, verify, etc) ()
+4. https_token | BENIGN | Tidak ada HTTPS token tersembunyi ()
+5. port | BENIGN | port = 0 (tidak ada indikator phishing) ()</t>
+        </is>
+      </c>
+      <c r="CJ36" t="inlineStr">
+        <is>
+          <t>URL yang Anda berikan, http://192.168.1.1/amazon-login@phishing-secure.com, dapat diklasifikasikan sebagai phishing karena beberapa alasan berikut:
+1. **Domain yang tidak jelas**: URL memiliki domain @phishing-secure.com, yang tidak terlihat seperti domain yang asli dari Amazon. Domain ini tampak seperti suatu percobaan untuk membuat orang percaya bahwa itu adalah situs resmi Amazon.
+2. **Alamat IP**: URL memiliki alamat IP, 192.168.1.1, yang biasanya digunakan untuk akses ke perangkat lunak router atau lainnya di jaringan lokal. Alamat IP ini tidak biasanya digunakan untuk akses ke situs internet.
+3. **Penggunaan karakter spesial**: URL menggunakan karakter "@" yang tidak biasanya digunakan dalam URL. karakter "@" biasanya digunakan untuk mengindikasikan bahwa ada suatu email atau alamat lain, bukan URL.
+4. **Penamaan file yang tidak jelas**: URL memiliki bagian "/amazon-login", yang tidak jelas apakah itu benar-benar adalah formulir login Amazon atau bukan.
+5. **Tampaknya seperti link palsu**: URL ini tampak seperti link palsu yang diciptakan untuk menipu orang untuk mengakses formulir login Amazon.
+Dengan demikian, URL ini dapat diklasifikasikan sebagai phishing karena memiliki beberapa ciri-ciri yang tidak biasa dan mungkin dapat menipu orang untuk mengakses formulir login palsu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>https://www.google.com</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>22</v>
+      </c>
+      <c r="F37" t="n">
+        <v>14</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>2</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>2</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH37" t="n">
+        <v>12</v>
+      </c>
+      <c r="BI37" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="BJ37" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="BK37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ37" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY37" t="n">
+        <v>1</v>
+      </c>
+      <c r="BZ37" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH37" t="inlineStr">
+        <is>
+          <t>🟢 URL terdeteksi sebagai BENIGN dengan phishing probability 33.38% (BENIGN Range: 0.00-0.60). Benign Confidence: 66.62%. Top features: length_words_raw (0.052), char_repeat (0.052), length_url (0.024), length_hostname (0.024), web_traffic (0.019). 1 fitur utama menunjukkan karakteristik website legitimate. Website ini AMAN untuk dikunjungi.</t>
+        </is>
+      </c>
+      <c r="CI37" t="inlineStr">
+        <is>
+          <t>1. length_words_raw | NEUTRAL | Tidak ada dampak signifikan (0.0518)
+2. char_repeat | NEUTRAL | Tidak ada dampak signifikan (0.0518)
+3. length_url | BENIGN | URL length normal (0.0239)
+4. length_hostname | NEUTRAL | Tidak ada dampak signifikan (0.0239)</t>
+        </is>
+      </c>
+      <c r="CJ37" t="inlineStr">
+        <is>
+          <t>URL `https://www.google.com` diklasifikasikan sebagai benign karena beberapa alasan:
+1. **Domain yang terpercaya**: Domain `google.com` adalah domain yang terpercaya dan dikenal sebagai perusahaan riset dan layanan online terkemuka. Domain ini tidak memiliki sejarah atau reputasi yang buruk.
+2. **Teks URL yang jelas**: URL mencantumkan alamat web secara jelas dan singkat, sehingga tidak ada potensi adware, virus, atau malware yang disembunyikan di dalam URL.
+3. **Koneksi HTTPS**: URL menggunakan HTTPS (Hypertext Transfer Protocol Secure) yang merupakan protokol keamanan yang aman untuk mengirimkan data secara online. Hal ini menunjukkan bahwa situs web ini menggunakan koneksi enkripsi untuk melindungi data pengunjung.
+4. **Kontent yang jelas**: Situs web Google adalah situs web yang jelas dan memiliki konten yang sesuai dengan nama domain. Konten di situs web ini tidak mencurigakan atau mencakup kode skrip yang dapat berisiko.
+5. **Tidak ada potensi iklan berbahaya**: Situs web Google tidak memiliki reputasi sebagai situs web yang menampilkan iklan berbahaya atau malfungsi. Iklan di situs web ini cenderung aman dan tidak akan mengancam perangkat pengunjung.
+Dengan demikian, URL `https://www.google.com` diklasifikasikan sebagai benign karena tidak memiliki potensi adware, virus, atau malware, serta tidak mencurigakan dalam hal koneksi, konten, atau reputasi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="57.6" customHeight="1">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>https://github.com</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>18</v>
+      </c>
+      <c r="F38" t="n">
+        <v>10</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH38" t="n">
+        <v>152</v>
+      </c>
+      <c r="BI38" t="n">
+        <v>0.9144736842105263</v>
+      </c>
+      <c r="BJ38" t="n">
+        <v>0.08552631578947369</v>
+      </c>
+      <c r="BK38" t="n">
+        <v>19</v>
+      </c>
+      <c r="BL38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO38" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP38" t="n">
+        <v>89.47368421052632</v>
+      </c>
+      <c r="BQ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR38" t="n">
+        <v>100</v>
+      </c>
+      <c r="BS38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU38" t="n">
+        <v>6.578947368421052</v>
+      </c>
+      <c r="BV38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY38" t="n">
+        <v>1</v>
+      </c>
+      <c r="BZ38" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH38" t="inlineStr">
+        <is>
+          <t>🟢 URL terdeteksi sebagai BENIGN dengan phishing probability 14.87% (BENIGN Range: 0.00-0.60). Benign Confidence: 85.13%. Top features: length_words_raw (0.047), char_repeat (0.047), length_url (0.023), length_hostname (0.023), dns_record (0.021). 1 fitur utama menunjukkan karakteristik website legitimate. Website ini AMAN untuk dikunjungi.</t>
+        </is>
+      </c>
+      <c r="CI38" s="1" t="inlineStr">
+        <is>
+          <t>1. length_words_raw | NEUTRAL | Tidak ada dampak signifikan (0.047)
+2. char_repeat | NEUTRAL | Tidak ada dampak signifikan (0.047)
+3. length_url | BENIGN | URL length normal (0.023)
+4. length_hostname | NEUTRAL | Tidak ada dampak signifikan (0.023)</t>
+        </is>
+      </c>
+      <c r="CJ38" t="inlineStr">
+        <is>
+          <t>URL `https://github.com` diklasifikasikan sebagai benign karena beberapa alasan:
+1. **Domain yang sah**: URL ini menggunakan domain yang sah dan terdaftar, yaitu `github.com`. Domain ini tidak mengandung kata-kata yang mencurigakan atau ekstensi file yang berbahaya.
+2. **Kehadiran dalam Internet**: GitHub adalah platform sumber terbuka yang telah ada sejak tahun 2008 dan sangat populer di kalangan pengembang perangkat lunak. Hal ini menunjukkan bahwa URL ini tidak berbahaya atau tidak sah.
+3. **Kegunaan umum**: URL ini digunakan oleh banyak orang sebagai platform untuk menghosting kode sumber, dokumentasi, dan proyek-proyek lainnya. Hal ini menunjukkan bahwa URL ini tidak memiliki tujuan berbahaya.
+4. **Kehadiran dalam database URL yang dicadangkan**: Beberapa database URL yang dicadangkan, seperti OpenPhish atau Feodotracker, tidak melaporkan `github.com` sebagai domain yang berbahaya. Hal ini juga menunjukkan bahwa URL ini tidak memiliki reputasi yang buruk.
+5. **Karakteristik yang umum**: URL ini memiliki karakteristik yang umum, seperti penggunaan HTTP, penggunaan dominasi, dan penggunaan karakter yang standar. Hal ini menunjukkan bahwa URL ini tidak memiliki tujuan untuk mengenkripsi konten atau untuk mengelabui pengguna.
+Dengan demikian, URL `https://github.com` dapat diklasifikasikan sebagai benign karena alasan-alasan di atas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>https://git-scm.com/docs</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>phishing</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>24</v>
+      </c>
+      <c r="F39" t="n">
+        <v>11</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>3</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH39" t="n">
+        <v>115</v>
+      </c>
+      <c r="BI39" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP39" t="n">
+        <v>25</v>
+      </c>
+      <c r="BQ39" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH39" t="inlineStr">
+        <is>
+          <t>🔴 URL terdeteksi sebagai PHISHING dengan phishing probability 88.54% (PHISHING Range: 0.60-1.00). Top features: char_repeat (0.041), length_words_raw (0.041), dns_record (0.016), google_index (0.016), avg_word_path (0.015). Website ini TIDAK AMAN untuk dikunjungi.</t>
+        </is>
+      </c>
+      <c r="CI39" t="inlineStr">
+        <is>
+          <t>1. char_repeat | NEUTRAL | Tidak ada dampak signifikan (0.0414)
+2. length_words_raw | NEUTRAL | Tidak ada dampak signifikan (0.0414)
+3. avg_word_path | NEUTRAL | Tidak ada dampak signifikan (0.0155)</t>
+        </is>
+      </c>
+      <c r="CJ39" t="inlineStr">
+        <is>
+          <t>URL yang Anda berikan tidak sepenuhnya benar sebagai phishing. URL tersebut adalah domain resmi untuk Git, suatu alat version control populer.
+Phishing biasanya mencoba menipu pengguna dengan membuat URL yang mirip dengan domain asli, tetapi sebenarnya adalah website palsu yang bertujuan untuk mencuri informasi sensitif seperti username dan password. Contoh URL phishing mungkin seperti:
+- https://git-scmdotcom/docs (tidak memiliki domain)
+- http://git-scm-dot-com/docs (kecuali ada domain, tapi domain utuh)
+- https://git-scmpal.com/docs (mirip dengan domain asli)
+Dalam kasus URL yang Anda berikan, https://git-scm.com/docs, tidak ada yang mencurigakan dan domain tersebut merupakan domain asli dari Git.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>https://github.com</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>18</v>
+      </c>
+      <c r="F40" t="n">
+        <v>10</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>2</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH40" t="n">
+        <v>152</v>
+      </c>
+      <c r="BI40" t="n">
+        <v>0.9144736842105263</v>
+      </c>
+      <c r="BJ40" t="n">
+        <v>0.08552631578947369</v>
+      </c>
+      <c r="BK40" t="n">
+        <v>19</v>
+      </c>
+      <c r="BL40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP40" t="n">
+        <v>89.47368421052632</v>
+      </c>
+      <c r="BQ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR40" t="n">
+        <v>100</v>
+      </c>
+      <c r="BS40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU40" t="n">
+        <v>6.578947368421052</v>
+      </c>
+      <c r="BV40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BZ40" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH40" t="inlineStr">
+        <is>
+          <t>🟢 URL terdeteksi sebagai BENIGN dengan phishing probability 14.87%. (SHAP) Top features: length_words_raw (0.047), char_repeat (0.047), length_url (0.023), length_hostname (0.023), dns_record (0.021). 1 fitur utama mendukung kondisi benign. Website ini AMAN untuk dikunjungi.</t>
+        </is>
+      </c>
+      <c r="CI40" t="inlineStr">
+        <is>
+          <t>1. length_words_raw | NEUTRAL | Tidak ada dampak signifikan (0.047)
+2. char_repeat | NEUTRAL | Tidak ada dampak signifikan (0.047)
+3. length_url | BENIGN | URL length normal (0.023)
+4. length_hostname | NEUTRAL | Tidak ada dampak signifikan (0.023)</t>
+        </is>
+      </c>
+      <c r="CJ40" t="inlineStr">
+        <is>
+          <t>Analisis teknis URL https://github.com dengan model Logistic Regression (Stacking) menunjukkan bahwa URL tersebut diklasifikasikan sebagai BENIGN dengan probabilitas phishing 14,87%. Berdasarkan fitur yang digunakan, tidak ada fitur yang memberikan kontribusi signifikan pada prediksi ini.
+Namun, jika keputusan berasal dari rule-based filter, mungkin terdapat aturan yang memicunya. Berikut adalah beberapa kemungkinan aturan:
+* Aturan 1: URL tidak memiliki kata-kata yang umum digunakan pada aksi phishing, seperti "login", "register", atau "verify".
+* Aturan 2: URL memiliki struktur yang umum digunakan oleh platform berbasis kode, seperti github.com.
+* Aturan 3: URL tidak memiliki tanda panah atau karakter spesial yang tidak biasa terlihat pada URL.
+Namun, perlu diingat bahwa rule-based filter dapat berbeda-beda tergantung pada implementasi dan konfigurasi yang digunakan. Jika keputusan berasal dari model Logistic Regression (Stacking), maka perlu memperhatikan hasil prediksi yang diberikan oleh model tersebut.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>https://www.apple.com</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>21</v>
+      </c>
+      <c r="F41" t="n">
+        <v>13</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>2</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>2</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH41" t="n">
+        <v>139</v>
+      </c>
+      <c r="BI41" t="n">
+        <v>0.7841726618705036</v>
+      </c>
+      <c r="BJ41" t="n">
+        <v>0.2158273381294964</v>
+      </c>
+      <c r="BK41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ41" t="n">
+        <v>43.15789473684211</v>
+      </c>
+      <c r="BR41" t="n">
+        <v>56.84210526315789</v>
+      </c>
+      <c r="BS41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY41" t="n">
+        <v>1</v>
+      </c>
+      <c r="BZ41" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH41" t="inlineStr">
+        <is>
+          <t>🟢 URL terdeteksi sebagai BENIGN dengan phishing probability 13.37%. (SHAP) Top features: length_words_raw (0.043), char_repeat (0.043), length_url (0.023), length_hostname (0.023), google_index (0.013). 1 fitur utama mendukung kondisi benign. Website ini AMAN untuk dikunjungi.</t>
+        </is>
+      </c>
+      <c r="CI41" t="inlineStr">
+        <is>
+          <t>1. length_words_raw | NEUTRAL | Tidak ada dampak signifikan (0.0434)
+2. char_repeat | NEUTRAL | Tidak ada dampak signifikan (0.0434)
+3. length_url | BENIGN | URL length normal (0.0233)
+4. length_hostname | NEUTRAL | Tidak ada dampak signifikan (0.0233)</t>
+        </is>
+      </c>
+      <c r="CJ41" t="inlineStr">
+        <is>
+          <t>Berikut adalah analisis singkat teknis:
+URL https://www.apple.com diklasifikasikan sebagai BENIGN karena memiliki panjang URL yang normal (nilai 21) dan tidak ada fitur lain yang memberikan kontribusi kuat terhadap probabilitas phishing, dengan probabilitas phishing sebesar 13.37%.
+(1) REKOMENDASI: IZINKAN URL https://www.apple.com, karena tidak menunjukkan ciri-ciri phishing.
+(2) Catatan: keputusan berdasarkan model Logistic Regression (Stacking) dan filter berbasis aturan yang dikembangkan menggunakan fitur-fitur URL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>http://paypal-verify-account-urgent.suspicious.tk</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>phishing</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>49</v>
+      </c>
+      <c r="F42" t="n">
+        <v>42</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>2</v>
+      </c>
+      <c r="I42" t="n">
+        <v>3</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>2</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>5.857142857142857</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>6.166666666666667</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF42" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG42" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF42" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH42" t="inlineStr">
+        <is>
+          <t>🔴 URL terdeteksi sebagai PHISHING dengan phishing probability 10.00%. 3 fitur utama menunjukkan indikator phishing berbahaya. Keputusan rule-based dipicu oleh: {'vi_count': 1, 'imp_count': 0, 'less_count': 1, 'vi_hits': ['suspicious_tld'], 'imp_hits': [], 'less_hits': ['length_hostname']}. Website ini TIDAK AMAN untuk dikunjungi.</t>
+        </is>
+      </c>
+      <c r="CI42" t="inlineStr">
+        <is>
+          <t>1. length_hostname | PHISHING | Hostname terlalu panjang ()
+2. phish_hints | PHISHING | Mengandung hint phishing (login, verify, etc) ()
+3. suspicious_tld | PHISHING | TLD mencurigakan ()
+4. length_url | BENIGN | URL length normal ()
+5. ip | BENIGN | ip = 0 (tidak ada indikator phishing) ()</t>
+        </is>
+      </c>
+      <c r="CJ42" t="inlineStr">
+        <is>
+          <t>Analisis singkat teknis menunjukkan bahwa URL: http://paypal-verify-account-urgent.suspicious.tk memiliki kecocokan tinggi dengan fitur-fitur yang biasa digunakan dalam phishing. Panjang hostname yang terlalu panjang (42 karakter), adanya hint phishing seperti "verify" dan "urgent", serta TLD yang mencurigakan ("suspicious") menunjukkan bahwa URL ini memiliki kemungkinan besar sebagai URL phishing.
+(1) KESIMPULAN TEGAS: REKOMENDASI: BLOKIR URL tersebut karena memiliki indikasi yang kuat sebagai phishing.
+(2) Catatan: keputusan berdasarkan model ML dan rule-based filter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>https://secure-login.verify.paypal.account-update.phishingsite.com</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>phishing</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>66</v>
+      </c>
+      <c r="F43" t="n">
+        <v>58</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>5</v>
+      </c>
+      <c r="I43" t="n">
+        <v>2</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>2</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>6.222222222222222</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>6.375</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD43" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA43" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB43" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC43" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD43" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE43" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF43" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH43" t="inlineStr">
+        <is>
+          <t>🔴 URL terdeteksi sebagai PHISHING dengan phishing probability 95.68%. (SHAP) Top features: length_hostname (2.067), nb_dots (1.975), nb_www (0.577), length_url (0.363), https_token (0.216). 2 fitur utama menunjukkan indikator phishing berbahaya. Website ini TIDAK AMAN untuk dikunjungi.</t>
+        </is>
+      </c>
+      <c r="CI43" t="inlineStr">
+        <is>
+          <t>1. length_hostname | PHISHING | Hostname terlalu panjang (2.0669)
+2. nb_dots | PHISHING | Banyak dot dalam URL (1.9751)
+3. nb_www | NEUTRAL | Tidak ada dampak signifikan (0.5769)
+4. length_url | NEUTRAL | Tidak ada dampak signifikan (0.3628)
+5. https_token | BENIGN | Tidak ada HTTPS token tersembunyi (0.2158)</t>
+        </is>
+      </c>
+      <c r="CJ43" t="inlineStr">
+        <is>
+          <t>Analisis teknis menunjukkan bahwa URL https://secure-login.verify.paypal.account-update.phishingsite.com diklasifikasikan sebagai PHISHING dengan probabilitas phishing 95.68% karena nilai fitur-fitur yang signifikan, seperti length_hostname (58) yang menunjukkan hostname terlalu panjang dan nb_dots (5) yang menunjukkan banyak dot dalam URL.
+KESIMPULAN TEGAS: REKOMENDASI: BLOKIR.
+Catatan: Penilaian berdasarkan model Logistic Regression (Stacking) dengan fitur-fitur yang direkrut dari rule-based filter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>http://192.168.1.1/amazon-login@phishing-secure.com</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>phishing</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>51</v>
+      </c>
+      <c r="F44" t="n">
+        <v>11</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" t="n">
+        <v>4</v>
+      </c>
+      <c r="I44" t="n">
+        <v>2</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>3</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>0.1568627450980392</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA44" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB44" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE44" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG44" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA44" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB44" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC44" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD44" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE44" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF44" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG44" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH44" t="inlineStr">
+        <is>
+          <t>🔴 URL terdeteksi sebagai PHISHING dengan phishing probability 0.00%. 3 fitur utama menunjukkan indikator phishing berbahaya. Keputusan rule-based dipicu oleh: {'vi_count': 2, 'imp_count': 0, 'less_count': 0, 'vi_hits': ['nb_at', 'ip'], 'imp_hits': [], 'less_hits': []}. Website ini TIDAK AMAN untuk dikunjungi.</t>
+        </is>
+      </c>
+      <c r="CI44" t="inlineStr">
+        <is>
+          <t>1. ip | PHISHING | IP address digunakan di URL ()
+2. nb_at | PHISHING | @ symbol dalam URL ()
+3. phish_hints | PHISHING | Mengandung hint phishing (login, verify, etc) ()
+4. https_token | BENIGN | Tidak ada HTTPS token tersembunyi ()
+5. port | BENIGN | port = 0 (tidak ada indikator phishing) ()</t>
+        </is>
+      </c>
+      <c r="CJ44" t="inlineStr">
+        <is>
+          <t>Analisis teknis terlalu singkat untuk memberikan kesimpulan yang pasti, namun berdasarkan fitur-fitur yang dijadikan patokan, dapat disimpulkan bahwa URL tersebut diklasifikasikan sebagai PHISHING karena:
+- Menggunakan IP address di URL (1) 
+- Mengandung @ symbol (1) 
+- Mengandung hint phishing (2) 
+Karena probabilitas phishing mencapai 95,00%, maka kita dapat mengeluarkan kesimpulan: "REKOMENDASI: BLOKIR" URL tersebut untuk mencegah kegiatan phishing.
+Catatan: keputusan berdasarkan model ML dan rule-based filter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>https://smmhejtkx.olghvlbkcdqtscd.top/ksjdbj</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>phishing</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>44</v>
+      </c>
+      <c r="F45" t="n">
+        <v>29</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>2</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>3</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF45" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG45" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA45" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB45" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC45" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD45" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE45" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF45" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG45" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH45" t="inlineStr">
+        <is>
+          <t>🔴 URL terdeteksi sebagai PHISHING dengan phishing probability 20.00%. 2 fitur utama menunjukkan indikator phishing berbahaya. Keputusan rule-based dipicu oleh: {'vi_count': 1, 'imp_count': 1, 'less_count': 0, 'vi_hits': ['suspicious_tld'], 'imp_hits': ['random_domain'], 'less_hits': []}. Website ini TIDAK AMAN untuk dikunjungi.</t>
+        </is>
+      </c>
+      <c r="CI45" t="inlineStr">
+        <is>
+          <t>1. random_domain | PHISHING | Domain terlihat random/tidak punya pola ()
+2. suspicious_tld | PHISHING | TLD mencurigakan ()
+3. length_url | BENIGN | URL length normal ()
+4. ip | BENIGN | ip = 0 (tidak ada indikator phishing) ()
+5. nb_at | BENIGN | nb_at = 0 (tidak ada indikator phishing) ()</t>
+        </is>
+      </c>
+      <c r="CJ45" t="inlineStr">
+        <is>
+          <t>Analisis singkat teknis:
+URL yang diberikan diklasifikasikan sebagai PHISHING karena memiliki beberapa fitur yang mencurigakan, yaitu random_domain (1) dan suspicious_tld (1), yang menambahkan probabilitas phishing menjadi 95,00%. Fitur lain seperti length_url (44) menunjukkan bahwa URL memiliki panjang normal, namun tidak cukup untuk mengimbangi fitur-fitur mencurigakan sebelumnya. IP address dalam URL tidak ditemukan, sehingga tidak memberikan indikator phishing.
+Kesimpulan Tegas: REKOMENDASI: BLOKIR, karena probabilitas phishing yang tinggi (95,00%). 
+Catatan: Keputusan berdasarkan model ML dan rule-based filter untuk mendeteksi phishing.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId1"/>

--- a/log_feature_extraction.xlsx
+++ b/log_feature_extraction.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CJ45"/>
+  <dimension ref="A1:CJ58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="3.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -13557,6 +13557,3685 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>https://www.google.com</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>22</v>
+      </c>
+      <c r="F46" t="n">
+        <v>14</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>2</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>2</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY46" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AZ46" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC46" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH46" t="n">
+        <v>12</v>
+      </c>
+      <c r="BI46" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="BJ46" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="BK46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ46" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY46" t="n">
+        <v>1</v>
+      </c>
+      <c r="BZ46" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH46" t="inlineStr">
+        <is>
+          <t>🟢 URL terdeteksi sebagai BENIGN dengan phishing probability 33.38%. (SHAP) Top features: length_words_raw (0.052), char_repeat (0.052), length_url (0.024), length_hostname (0.024), web_traffic (0.019). 1 fitur utama mendukung kondisi benign. Website ini AMAN untuk dikunjungi.</t>
+        </is>
+      </c>
+      <c r="CI46" t="inlineStr">
+        <is>
+          <t>1. length_words_raw | NEUTRAL | Tidak ada dampak signifikan (0.0518)
+2. char_repeat | NEUTRAL | Tidak ada dampak signifikan (0.0518)
+3. length_url | BENIGN | URL length normal (0.0239)
+4. length_hostname | NEUTRAL | Tidak ada dampak signifikan (0.0239)</t>
+        </is>
+      </c>
+      <c r="CJ46" t="inlineStr">
+        <is>
+          <t>Berikut adalah analisis singkat teknis pada URL tersebut:
+Tidak ada fitur kunci yang menunjukkan tanda-tanda phishing, seperti URL yang panjang atau hostname yang mencurigakan. Bahwa URL menunjukkan panjang normal dan tidak ada karakter yang terulang secara berlebihan. Dengan demikian, URL tersebut dapat diklasifikasikan sebagai BENIGN dengan probabilitas phishing 33,38%.
+(1) KESIMPULAN TEGAS: REKOMENDASI: IZINKAN.
+(2) Catatan: keputusan berdasarkan model ML dan rule-based filter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>https://www.google.com</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>22</v>
+      </c>
+      <c r="F47" t="n">
+        <v>14</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>2</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>2</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV47" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW47" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY47" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AZ47" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC47" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH47" t="n">
+        <v>12</v>
+      </c>
+      <c r="BI47" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="BJ47" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="BK47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ47" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY47" t="n">
+        <v>1</v>
+      </c>
+      <c r="BZ47" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH47" t="inlineStr">
+        <is>
+          <t>🟢 URL terdeteksi sebagai BENIGN dengan phishing probability 33.38%. (SHAP) Top features: length_words_raw (0.052), char_repeat (0.052), length_url (0.024), length_hostname (0.024), web_traffic (0.019). 1 fitur utama mendukung kondisi benign. Website ini AMAN untuk dikunjungi.</t>
+        </is>
+      </c>
+      <c r="CI47" t="inlineStr">
+        <is>
+          <t>1. length_words_raw | NEUTRAL | Tidak ada dampak signifikan (0.0518)
+2. char_repeat | NEUTRAL | Tidak ada dampak signifikan (0.0518)
+3. length_url | BENIGN | URL length normal (0.0239)
+4. length_hostname | NEUTRAL | Tidak ada dampak signifikan (0.0239)</t>
+        </is>
+      </c>
+      <c r="CJ47" t="inlineStr">
+        <is>
+          <t>Analisis singkat teknis URL https://www.google.com menunjukkan bahwa model Logistic Regression (Stacking) memberikan probabilitas phishing 33,38%, tetapi berdasarkan fitur-fitur yang dikaji, URL ini diklasifikasikan sebagai BENIGN karena panjang URL yang normal (22 karakter). Dengan demikian, rekomendasi tindakan yang tepat adalah 'REKOMENDASI: IZINKAN'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>https://www.microsoft.com</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>25</v>
+      </c>
+      <c r="F48" t="n">
+        <v>17</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>2</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>2</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV48" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW48" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY48" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ48" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB48" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC48" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH48" t="n">
+        <v>101</v>
+      </c>
+      <c r="BI48" t="n">
+        <v>0.5643564356435643</v>
+      </c>
+      <c r="BJ48" t="n">
+        <v>0.4356435643564356</v>
+      </c>
+      <c r="BK48" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP48" t="n">
+        <v>43.61702127659575</v>
+      </c>
+      <c r="BQ48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR48" t="n">
+        <v>100</v>
+      </c>
+      <c r="BS48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU48" t="n">
+        <v>1.98019801980198</v>
+      </c>
+      <c r="BV48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY48" t="n">
+        <v>1</v>
+      </c>
+      <c r="BZ48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH48" t="inlineStr">
+        <is>
+          <t>🟢 URL terdeteksi sebagai BENIGN dengan phishing probability 9.91%. (SHAP) Top features: length_words_raw (0.047), char_repeat (0.047), length_hostname (0.026), length_url (0.026), google_index (0.019). 1 fitur utama mendukung kondisi benign. Website ini AMAN untuk dikunjungi.</t>
+        </is>
+      </c>
+      <c r="CI48" t="inlineStr">
+        <is>
+          <t>1. length_words_raw | NEUTRAL | Tidak ada dampak signifikan (0.0466)
+2. char_repeat | NEUTRAL | Tidak ada dampak signifikan (0.0466)
+3. length_hostname | NEUTRAL | Tidak ada dampak signifikan (0.0256)
+4. length_url | BENIGN | URL length normal (0.0256)</t>
+        </is>
+      </c>
+      <c r="CJ48" t="inlineStr">
+        <is>
+          <t>Berikut adalah analisis singkat teknis mengapa URL https://www.microsoft.com diklasifikasikan sebagai BENIGN dengan probabilitas phishing 0.10:
+URL tersebut ditentukan sebagai BENIGN karena nilai fitur-fitur yang dihasilkan oleh model utama Logistic Regression (Stacking) tidak menunjukkan tanda-tanda phishing. Salah satu fitur yang mendukung kelas BENIGN adalah length_url (nilai: 25), yang menunjukkan bahwa URL memiliki panjang normal dan tidak memberikan dampak signifikan.
+REKOMENDASI: IZINKAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>http://paypal-verify-account-urgent.suspicious.tk</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>phishing</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>49</v>
+      </c>
+      <c r="F49" t="n">
+        <v>42</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>2</v>
+      </c>
+      <c r="I49" t="n">
+        <v>3</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>2</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" t="n">
+        <v>0</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0</v>
+      </c>
+      <c r="X49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ49" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV49" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW49" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY49" t="n">
+        <v>5.857142857142857</v>
+      </c>
+      <c r="AZ49" t="n">
+        <v>6.166666666666667</v>
+      </c>
+      <c r="BA49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB49" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD49" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF49" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG49" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ49" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA49" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB49" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC49" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD49" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE49" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF49" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG49" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH49" t="inlineStr">
+        <is>
+          <t>🔴 URL terdeteksi sebagai PHISHING dengan phishing probability 10.00%. 3 fitur utama menunjukkan indikator phishing berbahaya. Keputusan rule-based dipicu oleh: {'vi_count': 1, 'imp_count': 0, 'less_count': 1, 'vi_hits': ['suspicious_tld'], 'imp_hits': [], 'less_hits': ['length_hostname']}. Website ini TIDAK AMAN untuk dikunjungi.</t>
+        </is>
+      </c>
+      <c r="CI49" t="inlineStr">
+        <is>
+          <t>1. length_hostname | PHISHING | Hostname terlalu panjang ()
+2. phish_hints | PHISHING | Mengandung hint phishing (login, verify, etc) ()
+3. suspicious_tld | PHISHING | TLD mencurigakan ()
+4. length_url | BENIGN | URL length normal ()
+5. ip | BENIGN | ip = 0 (tidak ada indikator phishing) ()</t>
+        </is>
+      </c>
+      <c r="CJ49" t="inlineStr">
+        <is>
+          <t>Berikut analisis singkat teknis mengapa URL diklasifikasikan sebagai PHISHING dengan probabilitas phishing 0.95:
+URL tersebut diklasifikasikan sebagai PHISHING karena beberapa fitur yang memberikan kontribusi, yaitu hostname yang terlalu panjang (42 karakter), mengandung hint phishing (login, verify), dan menggunakan TLD mencurigakan. Sementara itu, fitur lain seperti panjang URL dan kehadiran IP tidak menunjukkan indikasi perilaku phishing.
+REKOMENDASI: BLOKIR</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>http://paypal-verify-account-urgent.suspicious.tk</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>phishing</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>49</v>
+      </c>
+      <c r="F50" t="n">
+        <v>42</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>2</v>
+      </c>
+      <c r="I50" t="n">
+        <v>3</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>2</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0</v>
+      </c>
+      <c r="X50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY50" t="n">
+        <v>5.857142857142857</v>
+      </c>
+      <c r="AZ50" t="n">
+        <v>6.166666666666667</v>
+      </c>
+      <c r="BA50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB50" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD50" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF50" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG50" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ50" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA50" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB50" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC50" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD50" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE50" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF50" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG50" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH50" t="inlineStr">
+        <is>
+          <t>🔴 URL terdeteksi sebagai PHISHING dengan phishing probability 10.00%. 3 fitur utama menunjukkan indikator phishing berbahaya. Keputusan rule-based dipicu oleh: {'vi_count': 1, 'imp_count': 0, 'less_count': 1, 'vi_hits': ['suspicious_tld'], 'imp_hits': [], 'less_hits': ['length_hostname']}. Website ini TIDAK AMAN untuk dikunjungi.</t>
+        </is>
+      </c>
+      <c r="CI50" t="inlineStr">
+        <is>
+          <t>1. length_hostname | PHISHING | Hostname terlalu panjang ()
+2. phish_hints | PHISHING | Mengandung hint phishing (login, verify, etc) ()
+3. suspicious_tld | PHISHING | TLD mencurigakan ()
+4. length_url | BENIGN | URL length normal ()
+5. ip | BENIGN | ip = 0 (tidak ada indikator phishing) ()</t>
+        </is>
+      </c>
+      <c r="CJ50" t="inlineStr">
+        <is>
+          <t>Berdasarkan analisis singkat teknis, URL diklasifikasikan sebagai PHISHING dengan probabilitas 0.95 karena beberapa fitur yang memberikan kontribusi, yaitu hostname yang terlalu panjang (42 karakter), mengandung hint phishing (login, verify, etc), dan TLD yang mencurigakan. Hasil analisis ini menjadikan URL sebagai sumber yang mencurigakan dan potensial melakukan penipuan.
+REKOMENDASI: BLOKIR</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>http://paypal-verify-account-urgent.suspicious.tk</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>phishing</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>49</v>
+      </c>
+      <c r="F51" t="n">
+        <v>42</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>2</v>
+      </c>
+      <c r="I51" t="n">
+        <v>3</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>2</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" t="n">
+        <v>0</v>
+      </c>
+      <c r="W51" t="n">
+        <v>0</v>
+      </c>
+      <c r="X51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ51" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR51" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT51" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV51" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW51" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY51" t="n">
+        <v>5.857142857142857</v>
+      </c>
+      <c r="AZ51" t="n">
+        <v>6.166666666666667</v>
+      </c>
+      <c r="BA51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB51" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD51" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF51" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG51" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ51" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA51" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB51" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC51" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD51" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE51" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF51" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG51" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH51" t="inlineStr">
+        <is>
+          <t>🔴 URL terdeteksi sebagai PHISHING dengan phishing probability 10.00%. 3 fitur utama menunjukkan indikator phishing berbahaya. Keputusan rule-based dipicu oleh: {'vi_count': 1, 'imp_count': 0, 'less_count': 1, 'vi_hits': ['suspicious_tld'], 'imp_hits': [], 'less_hits': ['length_hostname']}. Website ini TIDAK AMAN untuk dikunjungi.</t>
+        </is>
+      </c>
+      <c r="CI51" t="inlineStr">
+        <is>
+          <t>1. length_hostname | PHISHING | Hostname terlalu panjang ()
+2. phish_hints | PHISHING | Mengandung hint phishing (login, verify, etc) ()
+3. suspicious_tld | PHISHING | TLD mencurigakan ()
+4. length_url | BENIGN | URL length normal ()
+5. ip | BENIGN | ip = 0 (tidak ada indikator phishing) ()</t>
+        </is>
+      </c>
+      <c r="CJ51" t="inlineStr">
+        <is>
+          <t>Analisis singkat teknis menunjukkan bahwa URL http://paypal-verify-account-urgent.suspicious.tk diklasifikasikan sebagai PHISHING dengan probabilitas 0,95 karena beberapa fitur yang memberikan kontribusi. Hostname URL terlalu panjang (nilai 42) dan mengandung hint phishing (login, verify, etc) dengan nilai 3. Selain itu, TLD (Top-Level Domain) "suspicious.tk" juga mencurigakan. Karena nilai fitur PHISHING lebih tinggi daripada fitur BENIGN, URL ini kemungkinan besar merupakan phishing.
+REKOMENDASI: BLOKIR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>http://paypal-verify-account-urgent.suspicious.tk</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>phishing</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>49</v>
+      </c>
+      <c r="F52" t="n">
+        <v>42</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>2</v>
+      </c>
+      <c r="I52" t="n">
+        <v>3</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>2</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" t="n">
+        <v>0</v>
+      </c>
+      <c r="W52" t="n">
+        <v>0</v>
+      </c>
+      <c r="X52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ52" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR52" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS52" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT52" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV52" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW52" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY52" t="n">
+        <v>5.857142857142857</v>
+      </c>
+      <c r="AZ52" t="n">
+        <v>6.166666666666667</v>
+      </c>
+      <c r="BA52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB52" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD52" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF52" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG52" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH52" t="inlineStr">
+        <is>
+          <t>🔴 URL terdeteksi sebagai PHISHING dengan phishing probability 10.00%. 3 fitur utama menunjukkan indikator phishing berbahaya. Keputusan rule-based dipicu oleh: {'vi_count': 1, 'imp_count': 0, 'less_count': 1, 'vi_hits': ['suspicious_tld'], 'imp_hits': [], 'less_hits': ['length_hostname']}. Website ini TIDAK AMAN untuk dikunjungi.</t>
+        </is>
+      </c>
+      <c r="CI52" t="inlineStr">
+        <is>
+          <t>1. length_hostname | PHISHING | Hostname terlalu panjang ()
+2. phish_hints | PHISHING | Mengandung hint phishing (login, verify, etc) ()
+3. suspicious_tld | PHISHING | TLD mencurigakan ()
+4. length_url | BENIGN | URL length normal ()
+5. ip | BENIGN | ip = 0 (tidak ada indikator phishing) ()</t>
+        </is>
+      </c>
+      <c r="CJ52" t="inlineStr">
+        <is>
+          <t>Analisis singkat teknis:
+URL http://paypal-verify-account-urgent.suspicious.tk diklasifikasikan sebagai PHISHING karena terdapat beberapa kondisi yang tidak biasa, seperti:
+- Hostname yang terlalu panjang (42 karakter), yang tidak umum dalam domain yang valid.
+- Ternyata ada 3 hint phishing seperti "login" dan "verify" dalam nama URL.
+- TLD ("suspicious.tk") mencurigakan dan tidak umum digunakan.
+REKOMENDASI: BLOKIR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>https://smmhejtkx.olghvlbkcdqtscd.top/ksjdbj</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>phishing</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>44</v>
+      </c>
+      <c r="F53" t="n">
+        <v>29</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>2</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>3</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" t="n">
+        <v>0</v>
+      </c>
+      <c r="X53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ53" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR53" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS53" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT53" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU53" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV53" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW53" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX53" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY53" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ53" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA53" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF53" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG53" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH53" t="inlineStr">
+        <is>
+          <t>🔴 URL terdeteksi sebagai PHISHING dengan phishing probability 20.00%. 2 fitur utama menunjukkan indikator phishing berbahaya. Keputusan rule-based dipicu oleh: {'vi_count': 1, 'imp_count': 1, 'less_count': 0, 'vi_hits': ['suspicious_tld'], 'imp_hits': ['random_domain'], 'less_hits': []}. Website ini TIDAK AMAN untuk dikunjungi.</t>
+        </is>
+      </c>
+      <c r="CI53" t="inlineStr">
+        <is>
+          <t>1. random_domain | PHISHING | Domain terlihat random/tidak punya pola ()
+2. suspicious_tld | PHISHING | TLD mencurigakan ()
+3. length_url | BENIGN | URL length normal ()
+4. ip | BENIGN | ip = 0 (tidak ada indikator phishing) ()
+5. nb_at | BENIGN | nb_at = 0 (tidak ada indikator phishing) ()</t>
+        </is>
+      </c>
+      <c r="CJ53" t="inlineStr">
+        <is>
+          <t>Analisis singkat teknis menunjukkan bahwa URL diklasifikasikan sebagai PHISHING karena beberapa alasan:
+- Domain terlihat random dan tidak memiliki pola, sehingga nilai random_domain adalah 1.
+- TLD (Top-Level Domain) mencurigakan, sehingga nilai suspicious_tld adalah 1.
+- Namun, URL memiliki panjang normal dan tidak terdeteksi sebagai IP, sehingga tidak ada indikasi perilaku phishing lainnya.
+Dengan probabilitas phishing 0.95, rekomendasi adalah: REKOMENDASI: BLOKIR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>https://www.ietf.org/</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>21</v>
+      </c>
+      <c r="F54" t="n">
+        <v>12</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>2</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>3</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" t="n">
+        <v>0</v>
+      </c>
+      <c r="W54" t="n">
+        <v>0</v>
+      </c>
+      <c r="X54" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ54" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR54" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS54" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT54" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV54" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW54" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY54" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AZ54" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="BA54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH54" t="n">
+        <v>166</v>
+      </c>
+      <c r="BI54" t="n">
+        <v>0.8554216867469879</v>
+      </c>
+      <c r="BJ54" t="n">
+        <v>0.144578313253012</v>
+      </c>
+      <c r="BK54" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN54" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP54" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="BQ54" t="n">
+        <v>75</v>
+      </c>
+      <c r="BR54" t="n">
+        <v>25</v>
+      </c>
+      <c r="BS54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY54" t="n">
+        <v>1</v>
+      </c>
+      <c r="BZ54" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH54" t="inlineStr">
+        <is>
+          <t>🟢 URL terdeteksi sebagai BENIGN dengan phishing probability 5.08%. (SHAP) Top features: char_repeat (0.055), length_words_raw (0.055), length_url (0.022), length_hostname (0.022), google_index (0.020). 1 fitur utama mendukung kondisi benign. Website ini AMAN untuk dikunjungi.</t>
+        </is>
+      </c>
+      <c r="CI54" t="inlineStr">
+        <is>
+          <t>1. char_repeat | NEUTRAL | Tidak ada dampak signifikan (0.0555)
+2. length_words_raw | NEUTRAL | Tidak ada dampak signifikan (0.0555)
+3. length_url | BENIGN | URL length normal (0.0218)
+4. length_hostname | NEUTRAL | Tidak ada dampak signifikan (0.0218)</t>
+        </is>
+      </c>
+      <c r="CJ54" t="inlineStr">
+        <is>
+          <t>Berdasarkan analisis singkat teknis di atas, URL https://www.ietf.org/ diklasifikasikan sebagai BENIGN karena memenuhi kriteria URL length yang normal (21 karakter) dan tidak ada fitur lain yang memberikan kontribusi signifikan terhadap probabilitas phishing.
+REKOMENDASI: IZINKAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>https://www.python.org/downloads/</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>33</v>
+      </c>
+      <c r="F55" t="n">
+        <v>14</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>2</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>4</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" t="n">
+        <v>0</v>
+      </c>
+      <c r="W55" t="n">
+        <v>0</v>
+      </c>
+      <c r="X55" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ55" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT55" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU55" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV55" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW55" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX55" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY55" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AZ55" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA55" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH55" t="n">
+        <v>980</v>
+      </c>
+      <c r="BI55" t="n">
+        <v>0.6724489795918367</v>
+      </c>
+      <c r="BJ55" t="n">
+        <v>0.3275510204081633</v>
+      </c>
+      <c r="BK55" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP55" t="n">
+        <v>38.46153846153847</v>
+      </c>
+      <c r="BQ55" t="n">
+        <v>11.11111111111111</v>
+      </c>
+      <c r="BR55" t="n">
+        <v>88.88888888888889</v>
+      </c>
+      <c r="BS55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU55" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="BV55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY55" t="n">
+        <v>1</v>
+      </c>
+      <c r="BZ55" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH55" t="inlineStr">
+        <is>
+          <t>🟢 URL terdeteksi sebagai BENIGN dengan phishing probability 23.18%. (SHAP) Top features: length_words_raw (0.047), char_repeat (0.047), avg_word_path (0.015), phish_hints (0.015), google_index (0.014). Website ini AMAN untuk dikunjungi.</t>
+        </is>
+      </c>
+      <c r="CI55" t="inlineStr">
+        <is>
+          <t>1. length_words_raw | NEUTRAL | Tidak ada dampak signifikan (0.0474)
+2. char_repeat | NEUTRAL | Tidak ada dampak signifikan (0.0474)
+3. avg_word_path | NEUTRAL | Tidak ada dampak signifikan (0.0151)
+4. phish_hints | NEUTRAL | Tidak ada dampak signifikan (0.0151)</t>
+        </is>
+      </c>
+      <c r="CJ55" t="inlineStr">
+        <is>
+          <t>URL https://www.python.org/downloads/ diklasifikasikan sebagai BENIGN karena model Logistic Regression (Stacking) menunjukkan bahwa tidak ada fitur yang memberikan kontribusi signifikan pada probabilitas phishing. Tidak ada fitur yang menunjukkan perilaku yang mencurigakan. REKOMENDASI: IZINKAN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>https://account-security-microsoft365.com/validate/index.html</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>phishing</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>61</v>
+      </c>
+      <c r="F56" t="n">
+        <v>33</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>2</v>
+      </c>
+      <c r="I56" t="n">
+        <v>2</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>4</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" t="n">
+        <v>0</v>
+      </c>
+      <c r="W56" t="n">
+        <v>0</v>
+      </c>
+      <c r="X56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>0.04918032786885246</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ56" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR56" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT56" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU56" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV56" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW56" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX56" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY56" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AZ56" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BA56" t="n">
+        <v>5.666666666666667</v>
+      </c>
+      <c r="BB56" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC56" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG56" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH56" t="inlineStr">
+        <is>
+          <t>🔴 URL terdeteksi sebagai PHISHING dengan phishing probability 96.71%. (SHAP) Top features: page_rank (2.304), phish_hints (1.964), google_index (0.986), length_url (0.766), length_hostname (0.735). 2 fitur utama menunjukkan indikator phishing berbahaya. Website ini TIDAK AMAN untuk dikunjungi.</t>
+        </is>
+      </c>
+      <c r="CI56" t="inlineStr">
+        <is>
+          <t>1. phish_hints | PHISHING | Mengandung hint phishing (login, verify, etc) (1.9643)
+2. length_url | NEUTRAL | Tidak ada dampak signifikan (0.7661)
+3. length_hostname | PHISHING | Hostname terlalu panjang (0.7346)</t>
+        </is>
+      </c>
+      <c r="CJ56" t="inlineStr">
+        <is>
+          <t>Analisis singkat teknis:
+URL diklasifikasikan sebagai PHISHING karena fitur phish_hints yang bernilai 2 menunjukkan adanya hint phishing seperti "login" atau "verify", kemudian fitur length_hostname yang bernilai 33 menunjukkan hostname yang terlalu panjang, yang biasanya merupakan ciri-ciri domain palsu.
+REKOMENDASI: BLOKIR</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>https://office365-protect-mail.com/owa/auth</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>phishing</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>43</v>
+      </c>
+      <c r="F57" t="n">
+        <v>26</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I57" t="n">
+        <v>2</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>4</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" t="n">
+        <v>0</v>
+      </c>
+      <c r="W57" t="n">
+        <v>0</v>
+      </c>
+      <c r="X57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>0.06976744186046512</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0.1153846153846154</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ57" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR57" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT57" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU57" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV57" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW57" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX57" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY57" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ57" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="BA57" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BB57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG57" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH57" t="inlineStr">
+        <is>
+          <t>🔴 URL terdeteksi sebagai PHISHING dengan phishing probability 96.95%. (SHAP) Top features: page_rank (2.657), google_index (1.033), ratio_digits_host (0.759), nb_www (0.683), nb_hyperlinks (0.620). Website ini TIDAK AMAN untuk dikunjungi.</t>
+        </is>
+      </c>
+      <c r="CI57" t="inlineStr">
+        <is>
+          <t>1. ratio_digits_host | NEUTRAL | Tidak ada dampak signifikan (0.7591)
+2. nb_www | NEUTRAL | Tidak ada dampak signifikan (0.6826)</t>
+        </is>
+      </c>
+      <c r="CJ57" t="inlineStr">
+        <is>
+          <t>Analisis teknis menunjukkan bahwa URL https://office365-protect-mail.com/owa/auth diklasifikasikan sebagai PHISHING dengan probabilitas 0,97 karena model Logistic Regression (Stacking) tidak menemukan fitur utama yang signifikan. Model ini lebih fokus ke fitur-fitur lain yang tidak diketahui dalam informasi yang tersedia. REKOMENDASI: BLOKIR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>https://faturarenner.lojavirtual.com.br/?gclid=eaiaiqobchmi9ukc2pmr_qivcmqgch0ugg5_eaayasaaegjbb_d_bwe</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>phishing</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>102</v>
+      </c>
+      <c r="F58" t="n">
+        <v>31</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>3</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>1</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>1</v>
+      </c>
+      <c r="N58" t="n">
+        <v>4</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>3</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" t="n">
+        <v>0</v>
+      </c>
+      <c r="W58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>0.0392156862745098</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ58" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR58" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT58" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV58" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW58" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY58" t="n">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="AZ58" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX58" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ58" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA58" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB58" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC58" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD58" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE58" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF58" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG58" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH58" t="inlineStr">
+        <is>
+          <t>🔴 URL terdeteksi sebagai PHISHING dengan phishing probability 10.00%. 3 fitur utama menunjukkan indikator phishing berbahaya. Keputusan rule-based dipicu oleh: {'vi_count': 1, 'imp_count': 0, 'less_count': 1, 'vi_hits': ['nb_underscore'], 'imp_hits': [], 'less_hits': ['length_hostname']}. Website ini TIDAK AMAN untuk dikunjungi.</t>
+        </is>
+      </c>
+      <c r="CI58" t="inlineStr">
+        <is>
+          <t>1. length_url | PHISHING | URL terlalu panjang ()
+2. length_hostname | PHISHING | Hostname terlalu panjang ()
+3. nb_underscore | PHISHING | Banyak underscore dalam URL ()
+4. ip | BENIGN | ip = 0 (tidak ada indikator phishing) ()
+5. nb_at | BENIGN | nb_at = 0 (tidak ada indikator phishing) ()</t>
+        </is>
+      </c>
+      <c r="CJ58" t="inlineStr">
+        <is>
+          <t>Berikut adalah analisis singkat teknis mengapa URL diklasifikasikan sebagai PHISHING dengan probabilitas phishing 0.95:
+URL tersebut diklasifikasikan sebagai PHISHING karena beberapa fitur yang diidentifikasi oleh model Rule-Based Detection, seperti panjang URL (102 karakter) dan hostname (31 karakter) yang terlalu panjang, serta banyaknya underscore (4 kali) di dalam URL. Kombinasi dari fitur-fitur ini menempatkan URL tersebut pada kategor PHISHING dengan probabilitas tinggi.
+REKOMENDASI: BLOKIR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId1"/>
